--- a/research/traditional_assets/database/data/romania/romania_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_retail_distributors.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0878336651040466</v>
+        <v>0.08773093123988013</v>
       </c>
       <c r="C2">
-        <v>22.3</v>
+        <v>22.09008311680527</v>
       </c>
       <c r="D2">
-        <v>19.48</v>
+        <v>19.49308311680527</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.223</v>
       </c>
       <c r="G2">
         <v>2.82</v>
@@ -1445,28 +1445,28 @@
         <v>2.876</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0112169</v>
       </c>
       <c r="N2">
-        <v>2.876</v>
+        <v>2.8647831</v>
       </c>
       <c r="O2">
-        <v>0.46016</v>
+        <v>0.458365296</v>
       </c>
       <c r="P2">
-        <v>2.41584</v>
+        <v>2.406417804</v>
       </c>
       <c r="Q2">
-        <v>3.18984</v>
+        <v>3.180417804</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0878336651040466</v>
+        <v>0.0881903143837173</v>
       </c>
       <c r="T2">
-        <v>0.5786092218381922</v>
+        <v>0.5835186334174254</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>256.3988267703198</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08773093123988013</v>
+        <v>0.08762819737571365</v>
       </c>
       <c r="C3">
-        <v>22.09008311680527</v>
+        <v>21.88018381913231</v>
       </c>
       <c r="D3">
-        <v>19.49308311680527</v>
+        <v>19.50618381913231</v>
       </c>
       <c r="E3">
-        <v>0.223</v>
+        <v>0.446</v>
       </c>
       <c r="F3">
-        <v>0.223</v>
+        <v>0.446</v>
       </c>
       <c r="G3">
         <v>2.82</v>
@@ -1527,28 +1527,28 @@
         <v>2.876</v>
       </c>
       <c r="M3">
-        <v>0.0112169</v>
+        <v>0.0224338</v>
       </c>
       <c r="N3">
-        <v>2.8647831</v>
+        <v>2.8535662</v>
       </c>
       <c r="O3">
-        <v>0.458365296</v>
+        <v>0.456570592</v>
       </c>
       <c r="P3">
-        <v>2.406417804</v>
+        <v>2.396995608</v>
       </c>
       <c r="Q3">
-        <v>3.180417804</v>
+        <v>3.170995608</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0881903143837173</v>
+        <v>0.08855424222011596</v>
       </c>
       <c r="T3">
-        <v>0.5835186334174254</v>
+        <v>0.588528237069704</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>256.3988267703198</v>
+        <v>128.1994133851599</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08762819737571365</v>
+        <v>0.08752546351154716</v>
       </c>
       <c r="C4">
-        <v>21.88018381913231</v>
+        <v>21.67030214246103</v>
       </c>
       <c r="D4">
-        <v>19.50618381913231</v>
+        <v>19.51930214246103</v>
       </c>
       <c r="E4">
-        <v>0.446</v>
+        <v>0.669</v>
       </c>
       <c r="F4">
-        <v>0.446</v>
+        <v>0.669</v>
       </c>
       <c r="G4">
         <v>2.82</v>
@@ -1609,28 +1609,28 @@
         <v>2.876</v>
       </c>
       <c r="M4">
-        <v>0.0224338</v>
+        <v>0.0336507</v>
       </c>
       <c r="N4">
-        <v>2.8535662</v>
+        <v>2.8423493</v>
       </c>
       <c r="O4">
-        <v>0.456570592</v>
+        <v>0.454775888</v>
       </c>
       <c r="P4">
-        <v>2.396995608</v>
+        <v>2.387573412</v>
       </c>
       <c r="Q4">
-        <v>3.170995608</v>
+        <v>3.161573412</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08855424222011596</v>
+        <v>0.0889256737232445</v>
       </c>
       <c r="T4">
-        <v>0.588528237069704</v>
+        <v>0.5936411315189369</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>128.1994133851599</v>
+        <v>85.46627559010659</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08752546351154716</v>
+        <v>0.0874227296473807</v>
       </c>
       <c r="C5">
-        <v>21.67030214246103</v>
+        <v>21.46043812236686</v>
       </c>
       <c r="D5">
-        <v>19.51930214246103</v>
+        <v>19.53243812236686</v>
       </c>
       <c r="E5">
-        <v>0.669</v>
+        <v>0.892</v>
       </c>
       <c r="F5">
-        <v>0.669</v>
+        <v>0.892</v>
       </c>
       <c r="G5">
         <v>2.82</v>
@@ -1691,28 +1691,28 @@
         <v>2.876</v>
       </c>
       <c r="M5">
-        <v>0.0336507</v>
+        <v>0.0448676</v>
       </c>
       <c r="N5">
-        <v>2.8423493</v>
+        <v>2.8311324</v>
       </c>
       <c r="O5">
-        <v>0.454775888</v>
+        <v>0.452981184</v>
       </c>
       <c r="P5">
-        <v>2.387573412</v>
+        <v>2.378151216</v>
       </c>
       <c r="Q5">
-        <v>3.161573412</v>
+        <v>3.152151216</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0889256737232445</v>
+        <v>0.08930484338268824</v>
       </c>
       <c r="T5">
-        <v>0.5936411315189369</v>
+        <v>0.5988605446025289</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>85.46627559010659</v>
+        <v>64.09970669257994</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0874227296473807</v>
+        <v>0.08731999578321423</v>
       </c>
       <c r="C6">
-        <v>21.46043812236686</v>
+        <v>21.25059179452104</v>
       </c>
       <c r="D6">
-        <v>19.53243812236686</v>
+        <v>19.54559179452104</v>
       </c>
       <c r="E6">
-        <v>0.892</v>
+        <v>1.115</v>
       </c>
       <c r="F6">
-        <v>0.892</v>
+        <v>1.115</v>
       </c>
       <c r="G6">
         <v>2.82</v>
@@ -1773,28 +1773,28 @@
         <v>2.876</v>
       </c>
       <c r="M6">
-        <v>0.0448676</v>
+        <v>0.0560845</v>
       </c>
       <c r="N6">
-        <v>2.8311324</v>
+        <v>2.8199155</v>
       </c>
       <c r="O6">
-        <v>0.452981184</v>
+        <v>0.45118648</v>
       </c>
       <c r="P6">
-        <v>2.378151216</v>
+        <v>2.36872902</v>
       </c>
       <c r="Q6">
-        <v>3.152151216</v>
+        <v>3.14272902</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08930484338268824</v>
+        <v>0.08969199556127813</v>
       </c>
       <c r="T6">
-        <v>0.5988605446025289</v>
+        <v>0.6041898400668281</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>64.09970669257994</v>
+        <v>51.27976535406396</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08731999578321423</v>
+        <v>0.08721726191904774</v>
       </c>
       <c r="C7">
-        <v>21.25059179452104</v>
+        <v>21.04076319469097</v>
       </c>
       <c r="D7">
-        <v>19.54559179452104</v>
+        <v>19.55876319469098</v>
       </c>
       <c r="E7">
-        <v>1.115</v>
+        <v>1.338</v>
       </c>
       <c r="F7">
-        <v>1.115</v>
+        <v>1.338</v>
       </c>
       <c r="G7">
         <v>2.82</v>
@@ -1855,28 +1855,28 @@
         <v>2.876</v>
       </c>
       <c r="M7">
-        <v>0.0560845</v>
+        <v>0.0673014</v>
       </c>
       <c r="N7">
-        <v>2.8199155</v>
+        <v>2.8086986</v>
       </c>
       <c r="O7">
-        <v>0.45118648</v>
+        <v>0.449391776</v>
       </c>
       <c r="P7">
-        <v>2.36872902</v>
+        <v>2.359306824</v>
       </c>
       <c r="Q7">
-        <v>3.14272902</v>
+        <v>3.133306824</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08969199556127813</v>
+        <v>0.09008738502026356</v>
       </c>
       <c r="T7">
-        <v>0.6041898400668281</v>
+        <v>0.6096325247963251</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>51.27976535406396</v>
+        <v>42.7331377950533</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08721726191904774</v>
+        <v>0.08711452805488128</v>
       </c>
       <c r="C8">
-        <v>21.04076319469097</v>
+        <v>20.83095235874055</v>
       </c>
       <c r="D8">
-        <v>19.55876319469098</v>
+        <v>19.57195235874055</v>
       </c>
       <c r="E8">
-        <v>1.338</v>
+        <v>1.561</v>
       </c>
       <c r="F8">
-        <v>1.338</v>
+        <v>1.561</v>
       </c>
       <c r="G8">
         <v>2.82</v>
@@ -1937,28 +1937,28 @@
         <v>2.876</v>
       </c>
       <c r="M8">
-        <v>0.0673014</v>
+        <v>0.0785183</v>
       </c>
       <c r="N8">
-        <v>2.8086986</v>
+        <v>2.7974817</v>
       </c>
       <c r="O8">
-        <v>0.449391776</v>
+        <v>0.447597072</v>
       </c>
       <c r="P8">
-        <v>2.359306824</v>
+        <v>2.349884628</v>
       </c>
       <c r="Q8">
-        <v>3.133306824</v>
+        <v>3.123884628</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09008738502026356</v>
+        <v>0.09049127747836697</v>
       </c>
       <c r="T8">
-        <v>0.6096325247963251</v>
+        <v>0.6151922565092521</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>42.7331377950533</v>
+        <v>36.6284038243314</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08711452805488128</v>
+        <v>0.08701179419071481</v>
       </c>
       <c r="C9">
-        <v>20.83095235874055</v>
+        <v>20.62115932263044</v>
       </c>
       <c r="D9">
-        <v>19.57195235874055</v>
+        <v>19.58515932263044</v>
       </c>
       <c r="E9">
-        <v>1.561</v>
+        <v>1.784</v>
       </c>
       <c r="F9">
-        <v>1.561</v>
+        <v>1.784</v>
       </c>
       <c r="G9">
         <v>2.82</v>
@@ -2019,28 +2019,28 @@
         <v>2.876</v>
       </c>
       <c r="M9">
-        <v>0.0785183</v>
+        <v>0.0897352</v>
       </c>
       <c r="N9">
-        <v>2.7974817</v>
+        <v>2.7862648</v>
       </c>
       <c r="O9">
-        <v>0.447597072</v>
+        <v>0.445802368</v>
       </c>
       <c r="P9">
-        <v>2.349884628</v>
+        <v>2.340462432</v>
       </c>
       <c r="Q9">
-        <v>3.123884628</v>
+        <v>3.114462432</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09049127747836697</v>
+        <v>0.09090395020729869</v>
       </c>
       <c r="T9">
-        <v>0.6151922565092521</v>
+        <v>0.6208728519550688</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.6284038243314</v>
+        <v>32.04985334628998</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08701179419071481</v>
+        <v>0.08690906032654833</v>
       </c>
       <c r="C10">
-        <v>20.62115932263044</v>
+        <v>20.41138412241845</v>
       </c>
       <c r="D10">
-        <v>19.58515932263044</v>
+        <v>19.59838412241845</v>
       </c>
       <c r="E10">
-        <v>1.784</v>
+        <v>2.007</v>
       </c>
       <c r="F10">
-        <v>1.784</v>
+        <v>2.007</v>
       </c>
       <c r="G10">
         <v>2.82</v>
@@ -2101,28 +2101,28 @@
         <v>2.876</v>
       </c>
       <c r="M10">
-        <v>0.0897352</v>
+        <v>0.1009521</v>
       </c>
       <c r="N10">
-        <v>2.7862648</v>
+        <v>2.7750479</v>
       </c>
       <c r="O10">
-        <v>0.445802368</v>
+        <v>0.444007664</v>
       </c>
       <c r="P10">
-        <v>2.340462432</v>
+        <v>2.331040236</v>
       </c>
       <c r="Q10">
-        <v>3.114462432</v>
+        <v>3.105040236</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09090395020729869</v>
+        <v>0.09132569266653662</v>
       </c>
       <c r="T10">
-        <v>0.6208728519550688</v>
+        <v>0.6266782956524419</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>32.04985334628998</v>
+        <v>28.48875853003553</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08690906032654833</v>
+        <v>0.08680632646238186</v>
       </c>
       <c r="C11">
-        <v>20.41138412241845</v>
+        <v>20.20162679425986</v>
       </c>
       <c r="D11">
-        <v>19.59838412241845</v>
+        <v>19.61162679425986</v>
       </c>
       <c r="E11">
-        <v>2.007</v>
+        <v>2.23</v>
       </c>
       <c r="F11">
-        <v>2.007</v>
+        <v>2.23</v>
       </c>
       <c r="G11">
         <v>2.82</v>
@@ -2183,28 +2183,28 @@
         <v>2.876</v>
       </c>
       <c r="M11">
-        <v>0.1009521</v>
+        <v>0.112169</v>
       </c>
       <c r="N11">
-        <v>2.7750479</v>
+        <v>2.763831</v>
       </c>
       <c r="O11">
-        <v>0.444007664</v>
+        <v>0.44221296</v>
       </c>
       <c r="P11">
-        <v>2.331040236</v>
+        <v>2.32161804</v>
       </c>
       <c r="Q11">
-        <v>3.105040236</v>
+        <v>3.09561804</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09132569266653662</v>
+        <v>0.09175680718042428</v>
       </c>
       <c r="T11">
-        <v>0.6266782956524419</v>
+        <v>0.6326127492097567</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.48875853003553</v>
+        <v>25.63988267703198</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08680632646238186</v>
+        <v>0.08670359259821538</v>
       </c>
       <c r="C12">
-        <v>20.20162679425986</v>
+        <v>19.99188737440774</v>
       </c>
       <c r="D12">
-        <v>19.61162679425986</v>
+        <v>19.62488737440773</v>
       </c>
       <c r="E12">
-        <v>2.23</v>
+        <v>2.453</v>
       </c>
       <c r="F12">
-        <v>2.23</v>
+        <v>2.453</v>
       </c>
       <c r="G12">
         <v>2.82</v>
@@ -2265,28 +2265,28 @@
         <v>2.876</v>
       </c>
       <c r="M12">
-        <v>0.112169</v>
+        <v>0.1233859</v>
       </c>
       <c r="N12">
-        <v>2.763831</v>
+        <v>2.7526141</v>
       </c>
       <c r="O12">
-        <v>0.44221296</v>
+        <v>0.440418256</v>
       </c>
       <c r="P12">
-        <v>2.32161804</v>
+        <v>2.312195844</v>
       </c>
       <c r="Q12">
-        <v>3.09561804</v>
+        <v>3.086195844</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09175680718042428</v>
+        <v>0.09219760966091615</v>
       </c>
       <c r="T12">
-        <v>0.6326127492097567</v>
+        <v>0.6386805612739775</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.63988267703198</v>
+        <v>23.30898425184725</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08670359259821538</v>
+        <v>0.08660085873404891</v>
       </c>
       <c r="C13">
-        <v>19.99188737440774</v>
+        <v>19.78216589921322</v>
       </c>
       <c r="D13">
-        <v>19.62488737440773</v>
+        <v>19.63816589921322</v>
       </c>
       <c r="E13">
-        <v>2.453</v>
+        <v>2.676</v>
       </c>
       <c r="F13">
-        <v>2.453</v>
+        <v>2.676</v>
       </c>
       <c r="G13">
         <v>2.82</v>
@@ -2347,28 +2347,28 @@
         <v>2.876</v>
       </c>
       <c r="M13">
-        <v>0.1233859</v>
+        <v>0.1346028</v>
       </c>
       <c r="N13">
-        <v>2.7526141</v>
+        <v>2.7413972</v>
       </c>
       <c r="O13">
-        <v>0.440418256</v>
+        <v>0.438623552</v>
       </c>
       <c r="P13">
-        <v>2.312195844</v>
+        <v>2.302773648</v>
       </c>
       <c r="Q13">
-        <v>3.086195844</v>
+        <v>3.076773648</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09219760966091615</v>
+        <v>0.09264843037960102</v>
       </c>
       <c r="T13">
-        <v>0.6386805612739775</v>
+        <v>0.6448862781578396</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.30898425184725</v>
+        <v>21.36656889752665</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08660085873404891</v>
+        <v>0.08649812486988243</v>
       </c>
       <c r="C14">
-        <v>19.78216589921322</v>
+        <v>19.57246240512596</v>
       </c>
       <c r="D14">
-        <v>19.63816589921322</v>
+        <v>19.65146240512596</v>
       </c>
       <c r="E14">
-        <v>2.676</v>
+        <v>2.899</v>
       </c>
       <c r="F14">
-        <v>2.676</v>
+        <v>2.899</v>
       </c>
       <c r="G14">
         <v>2.82</v>
@@ -2429,28 +2429,28 @@
         <v>2.876</v>
       </c>
       <c r="M14">
-        <v>0.1346028</v>
+        <v>0.1458197</v>
       </c>
       <c r="N14">
-        <v>2.7413972</v>
+        <v>2.7301803</v>
       </c>
       <c r="O14">
-        <v>0.438623552</v>
+        <v>0.436828848</v>
       </c>
       <c r="P14">
-        <v>2.302773648</v>
+        <v>2.293351452</v>
       </c>
       <c r="Q14">
-        <v>3.076773648</v>
+        <v>3.067351452</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09264843037960102</v>
+        <v>0.09310961479296831</v>
       </c>
       <c r="T14">
-        <v>0.6448862781578396</v>
+        <v>0.6512346551999515</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.36656889752665</v>
+        <v>19.72298667463998</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08649812486988243</v>
+        <v>0.08639539100571594</v>
       </c>
       <c r="C15">
-        <v>19.57246240512596</v>
+        <v>19.36277692869436</v>
       </c>
       <c r="D15">
-        <v>19.65146240512596</v>
+        <v>19.66477692869436</v>
       </c>
       <c r="E15">
-        <v>2.899</v>
+        <v>3.122</v>
       </c>
       <c r="F15">
-        <v>2.899</v>
+        <v>3.122</v>
       </c>
       <c r="G15">
         <v>2.82</v>
@@ -2511,28 +2511,28 @@
         <v>2.876</v>
       </c>
       <c r="M15">
-        <v>0.1458197</v>
+        <v>0.1570366</v>
       </c>
       <c r="N15">
-        <v>2.7301803</v>
+        <v>2.7189634</v>
       </c>
       <c r="O15">
-        <v>0.436828848</v>
+        <v>0.435034144</v>
       </c>
       <c r="P15">
-        <v>2.293351452</v>
+        <v>2.283929256</v>
       </c>
       <c r="Q15">
-        <v>3.067351452</v>
+        <v>3.057929256</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09310961479296831</v>
+        <v>0.09358152442525111</v>
       </c>
       <c r="T15">
-        <v>0.6512346551999515</v>
+        <v>0.6577306689174613</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.72298667463998</v>
+        <v>18.3142019121657</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08639539100571594</v>
+        <v>0.08629265714154948</v>
       </c>
       <c r="C16">
-        <v>19.36277692869436</v>
+        <v>19.15310950656592</v>
       </c>
       <c r="D16">
-        <v>19.66477692869436</v>
+        <v>19.67810950656592</v>
       </c>
       <c r="E16">
-        <v>3.122</v>
+        <v>3.345000000000001</v>
       </c>
       <c r="F16">
-        <v>3.122</v>
+        <v>3.345000000000001</v>
       </c>
       <c r="G16">
         <v>2.82</v>
@@ -2593,28 +2593,28 @@
         <v>2.876</v>
       </c>
       <c r="M16">
-        <v>0.1570366</v>
+        <v>0.1682535</v>
       </c>
       <c r="N16">
-        <v>2.7189634</v>
+        <v>2.7077465</v>
       </c>
       <c r="O16">
-        <v>0.435034144</v>
+        <v>0.43323944</v>
       </c>
       <c r="P16">
-        <v>2.283929256</v>
+        <v>2.27450706</v>
       </c>
       <c r="Q16">
-        <v>3.057929256</v>
+        <v>3.04850706</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09358152442525111</v>
+        <v>0.09406453781358762</v>
       </c>
       <c r="T16">
-        <v>0.6577306689174613</v>
+        <v>0.6643795300165595</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.3142019121657</v>
+        <v>17.09325511802131</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08629265714154948</v>
+        <v>0.08618992327738299</v>
       </c>
       <c r="C17">
-        <v>19.15310950656592</v>
+        <v>18.94346017548764</v>
       </c>
       <c r="D17">
-        <v>19.67810950656592</v>
+        <v>19.69146017548765</v>
       </c>
       <c r="E17">
-        <v>3.345</v>
+        <v>3.568</v>
       </c>
       <c r="F17">
-        <v>3.345</v>
+        <v>3.568</v>
       </c>
       <c r="G17">
         <v>2.82</v>
@@ -2675,28 +2675,28 @@
         <v>2.876</v>
       </c>
       <c r="M17">
-        <v>0.1682535</v>
+        <v>0.1794704</v>
       </c>
       <c r="N17">
-        <v>2.7077465</v>
+        <v>2.6965296</v>
       </c>
       <c r="O17">
-        <v>0.43323944</v>
+        <v>0.431444736</v>
       </c>
       <c r="P17">
-        <v>2.27450706</v>
+        <v>2.265084864</v>
       </c>
       <c r="Q17">
-        <v>3.04850706</v>
+        <v>3.039084864</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09406453781358762</v>
+        <v>0.09455905152069405</v>
       </c>
       <c r="T17">
-        <v>0.6643795300165595</v>
+        <v>0.6711866973323029</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>17.09325511802132</v>
+        <v>16.02492667314499</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08618992327738299</v>
+        <v>0.08608718941321652</v>
       </c>
       <c r="C18">
-        <v>18.94346017548764</v>
+        <v>18.7338289723063</v>
       </c>
       <c r="D18">
-        <v>19.69146017548765</v>
+        <v>19.7048289723063</v>
       </c>
       <c r="E18">
-        <v>3.568</v>
+        <v>3.791</v>
       </c>
       <c r="F18">
-        <v>3.568</v>
+        <v>3.791</v>
       </c>
       <c r="G18">
         <v>2.82</v>
@@ -2757,28 +2757,28 @@
         <v>2.876</v>
       </c>
       <c r="M18">
-        <v>0.1794704</v>
+        <v>0.1906873</v>
       </c>
       <c r="N18">
-        <v>2.6965296</v>
+        <v>2.6853127</v>
       </c>
       <c r="O18">
-        <v>0.431444736</v>
+        <v>0.429650032</v>
       </c>
       <c r="P18">
-        <v>2.265084864</v>
+        <v>2.255662668</v>
       </c>
       <c r="Q18">
-        <v>3.039084864</v>
+        <v>3.029662668</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09455905152069405</v>
+        <v>0.09506548122074281</v>
       </c>
       <c r="T18">
-        <v>0.6711866973323029</v>
+        <v>0.6781578927761366</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>16.02492667314499</v>
+        <v>15.08228392766587</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08608718941321652</v>
+        <v>0.08598445554905004</v>
       </c>
       <c r="C19">
-        <v>18.7338289723063</v>
+        <v>18.52421593396878</v>
       </c>
       <c r="D19">
-        <v>19.7048289723063</v>
+        <v>19.71821593396878</v>
       </c>
       <c r="E19">
-        <v>3.791</v>
+        <v>4.014</v>
       </c>
       <c r="F19">
-        <v>3.791</v>
+        <v>4.014</v>
       </c>
       <c r="G19">
         <v>2.82</v>
@@ -2839,28 +2839,28 @@
         <v>2.876</v>
       </c>
       <c r="M19">
-        <v>0.1906873</v>
+        <v>0.2019042</v>
       </c>
       <c r="N19">
-        <v>2.6853127</v>
+        <v>2.6740958</v>
       </c>
       <c r="O19">
-        <v>0.429650032</v>
+        <v>0.427855328</v>
       </c>
       <c r="P19">
-        <v>2.255662668</v>
+        <v>2.246240472</v>
       </c>
       <c r="Q19">
-        <v>3.029662668</v>
+        <v>3.020240472</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09506548122074281</v>
+        <v>0.09558426286469518</v>
       </c>
       <c r="T19">
-        <v>0.6781578927761366</v>
+        <v>0.6852991173771369</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>15.08228392766587</v>
+        <v>14.24437926501776</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08598445554905006</v>
+        <v>0.08588172168488359</v>
       </c>
       <c r="C20">
-        <v>18.52421593396878</v>
+        <v>18.31462109752247</v>
       </c>
       <c r="D20">
-        <v>19.71821593396878</v>
+        <v>19.73162109752247</v>
       </c>
       <c r="E20">
-        <v>4.014</v>
+        <v>4.237</v>
       </c>
       <c r="F20">
-        <v>4.014</v>
+        <v>4.237</v>
       </c>
       <c r="G20">
         <v>2.82</v>
@@ -2921,28 +2921,28 @@
         <v>2.876</v>
       </c>
       <c r="M20">
-        <v>0.2019042</v>
+        <v>0.2131211</v>
       </c>
       <c r="N20">
-        <v>2.6740958</v>
+        <v>2.6628789</v>
       </c>
       <c r="O20">
-        <v>0.427855328</v>
+        <v>0.426060624</v>
       </c>
       <c r="P20">
-        <v>2.246240472</v>
+        <v>2.236818276</v>
       </c>
       <c r="Q20">
-        <v>3.020240472</v>
+        <v>3.010818276</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09558426286469518</v>
+        <v>0.09611585393195504</v>
       </c>
       <c r="T20">
-        <v>0.6852991173771369</v>
+        <v>0.6926166685114952</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.24437926501776</v>
+        <v>13.49467509317472</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08588172168488359</v>
+        <v>0.08603098782071711</v>
       </c>
       <c r="C21">
-        <v>18.31462109752247</v>
+        <v>18.07215019131903</v>
       </c>
       <c r="D21">
-        <v>19.73162109752247</v>
+        <v>19.71215019131903</v>
       </c>
       <c r="E21">
-        <v>4.237</v>
+        <v>4.46</v>
       </c>
       <c r="F21">
-        <v>4.237</v>
+        <v>4.46</v>
       </c>
       <c r="G21">
         <v>2.82</v>
@@ -3003,45 +3003,45 @@
         <v>2.876</v>
       </c>
       <c r="M21">
-        <v>0.2131211</v>
+        <v>0.231028</v>
       </c>
       <c r="N21">
-        <v>2.6628789</v>
+        <v>2.644972</v>
       </c>
       <c r="O21">
-        <v>0.426060624</v>
+        <v>0.42319552</v>
       </c>
       <c r="P21">
-        <v>2.236818276</v>
+        <v>2.22177648</v>
       </c>
       <c r="Q21">
-        <v>3.010818276</v>
+        <v>2.99577648</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09611585393195504</v>
+        <v>0.09666073477589637</v>
       </c>
       <c r="T21">
-        <v>0.6926166685114952</v>
+        <v>0.7001171584242125</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.16</v>
       </c>
       <c r="W21">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.49467509317472</v>
+        <v>12.44870751597209</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08603098782071711</v>
+        <v>0.08594085395655063</v>
       </c>
       <c r="C22">
-        <v>18.07215019131903</v>
+        <v>17.86090303491018</v>
       </c>
       <c r="D22">
-        <v>19.71215019131903</v>
+        <v>19.72390303491018</v>
       </c>
       <c r="E22">
-        <v>4.46</v>
+        <v>4.683000000000001</v>
       </c>
       <c r="F22">
-        <v>4.46</v>
+        <v>4.683000000000001</v>
       </c>
       <c r="G22">
         <v>2.82</v>
@@ -3085,28 +3085,28 @@
         <v>2.876</v>
       </c>
       <c r="M22">
-        <v>0.231028</v>
+        <v>0.2425794</v>
       </c>
       <c r="N22">
-        <v>2.644972</v>
+        <v>2.6334206</v>
       </c>
       <c r="O22">
-        <v>0.42319552</v>
+        <v>0.421347296</v>
       </c>
       <c r="P22">
-        <v>2.22177648</v>
+        <v>2.212073304</v>
       </c>
       <c r="Q22">
-        <v>2.99577648</v>
+        <v>2.986073304</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09666073477589637</v>
+        <v>0.09721941007158308</v>
       </c>
       <c r="T22">
-        <v>0.7001171584242125</v>
+        <v>0.707807534157505</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.44870751597209</v>
+        <v>11.85591191997342</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08594085395655063</v>
+        <v>0.08585072009238415</v>
       </c>
       <c r="C23">
-        <v>17.86090303491018</v>
+        <v>17.64966990150097</v>
       </c>
       <c r="D23">
-        <v>19.72390303491018</v>
+        <v>19.73566990150097</v>
       </c>
       <c r="E23">
-        <v>4.683</v>
+        <v>4.906000000000001</v>
       </c>
       <c r="F23">
-        <v>4.683</v>
+        <v>4.906000000000001</v>
       </c>
       <c r="G23">
         <v>2.82</v>
@@ -3167,28 +3167,28 @@
         <v>2.876</v>
       </c>
       <c r="M23">
-        <v>0.2425794</v>
+        <v>0.2541308</v>
       </c>
       <c r="N23">
-        <v>2.6334206</v>
+        <v>2.6218692</v>
       </c>
       <c r="O23">
-        <v>0.421347296</v>
+        <v>0.419499072</v>
       </c>
       <c r="P23">
-        <v>2.212073304</v>
+        <v>2.202370128</v>
       </c>
       <c r="Q23">
-        <v>2.986073304</v>
+        <v>2.976370128</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09721941007158308</v>
+        <v>0.09779241037485148</v>
       </c>
       <c r="T23">
-        <v>0.707807534157505</v>
+        <v>0.7156950990121638</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.85591191997342</v>
+        <v>11.3170068327019</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08585072009238415</v>
+        <v>0.08576058622821768</v>
       </c>
       <c r="C24">
-        <v>17.64966990150097</v>
+        <v>17.43845081620386</v>
       </c>
       <c r="D24">
-        <v>19.73566990150097</v>
+        <v>19.74745081620387</v>
       </c>
       <c r="E24">
-        <v>4.906000000000001</v>
+        <v>5.129</v>
       </c>
       <c r="F24">
-        <v>4.906000000000001</v>
+        <v>5.129</v>
       </c>
       <c r="G24">
         <v>2.82</v>
@@ -3249,28 +3249,28 @@
         <v>2.876</v>
       </c>
       <c r="M24">
-        <v>0.2541308</v>
+        <v>0.2656822</v>
       </c>
       <c r="N24">
-        <v>2.6218692</v>
+        <v>2.6103178</v>
       </c>
       <c r="O24">
-        <v>0.419499072</v>
+        <v>0.417650848</v>
       </c>
       <c r="P24">
-        <v>2.202370128</v>
+        <v>2.192666952</v>
       </c>
       <c r="Q24">
-        <v>2.976370128</v>
+        <v>2.966666952</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09779241037485148</v>
+        <v>0.0983802938028801</v>
       </c>
       <c r="T24">
-        <v>0.7156950990121638</v>
+        <v>0.7237875356812296</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.3170068327019</v>
+        <v>10.82496305736703</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08576058622821768</v>
+        <v>0.08567045236405121</v>
       </c>
       <c r="C25">
-        <v>17.43845081620386</v>
+        <v>17.22724580419133</v>
       </c>
       <c r="D25">
-        <v>19.74745081620387</v>
+        <v>19.75924580419133</v>
       </c>
       <c r="E25">
-        <v>5.129</v>
+        <v>5.352</v>
       </c>
       <c r="F25">
-        <v>5.129</v>
+        <v>5.352</v>
       </c>
       <c r="G25">
         <v>2.82</v>
@@ -3331,28 +3331,28 @@
         <v>2.876</v>
       </c>
       <c r="M25">
-        <v>0.2656822</v>
+        <v>0.2772336</v>
       </c>
       <c r="N25">
-        <v>2.6103178</v>
+        <v>2.5987664</v>
       </c>
       <c r="O25">
-        <v>0.417650848</v>
+        <v>0.415802624</v>
       </c>
       <c r="P25">
-        <v>2.192666952</v>
+        <v>2.182963776</v>
       </c>
       <c r="Q25">
-        <v>2.966666952</v>
+        <v>2.956963776</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0983802938028801</v>
+        <v>0.0989836478474358</v>
       </c>
       <c r="T25">
-        <v>0.7237875356812296</v>
+        <v>0.7320929312100074</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.82496305736703</v>
+        <v>10.37392292997674</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08567045236405121</v>
+        <v>0.08558031849988473</v>
       </c>
       <c r="C26">
-        <v>17.22724580419133</v>
+        <v>17.016054890696</v>
       </c>
       <c r="D26">
-        <v>19.75924580419133</v>
+        <v>19.771054890696</v>
       </c>
       <c r="E26">
-        <v>5.352</v>
+        <v>5.575</v>
       </c>
       <c r="F26">
-        <v>5.352</v>
+        <v>5.575</v>
       </c>
       <c r="G26">
         <v>2.82</v>
@@ -3413,28 +3413,28 @@
         <v>2.876</v>
       </c>
       <c r="M26">
-        <v>0.2772336</v>
+        <v>0.288785</v>
       </c>
       <c r="N26">
-        <v>2.5987664</v>
+        <v>2.587215</v>
       </c>
       <c r="O26">
-        <v>0.415802624</v>
+        <v>0.4139544</v>
       </c>
       <c r="P26">
-        <v>2.182963776</v>
+        <v>2.1732606</v>
       </c>
       <c r="Q26">
-        <v>2.956963776</v>
+        <v>2.9472606</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.0989836478474358</v>
+        <v>0.09960309133317966</v>
       </c>
       <c r="T26">
-        <v>0.7320929312100074</v>
+        <v>0.7406198039528861</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.37392292997674</v>
+        <v>9.958966012777672</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08558031849988473</v>
+        <v>0.08586146463571825</v>
       </c>
       <c r="C27">
-        <v>17.016054890696</v>
+        <v>16.75626647739942</v>
       </c>
       <c r="D27">
-        <v>19.771054890696</v>
+        <v>19.73426647739942</v>
       </c>
       <c r="E27">
-        <v>5.575</v>
+        <v>5.798</v>
       </c>
       <c r="F27">
-        <v>5.575</v>
+        <v>5.798</v>
       </c>
       <c r="G27">
         <v>2.82</v>
@@ -3495,45 +3495,45 @@
         <v>2.876</v>
       </c>
       <c r="M27">
-        <v>0.288785</v>
+        <v>0.310193</v>
       </c>
       <c r="N27">
-        <v>2.587215</v>
+        <v>2.565807</v>
       </c>
       <c r="O27">
-        <v>0.4139544</v>
+        <v>0.41052912</v>
       </c>
       <c r="P27">
-        <v>2.1732606</v>
+        <v>2.15527788</v>
       </c>
       <c r="Q27">
-        <v>2.9472606</v>
+        <v>2.92927788</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09960309133317966</v>
+        <v>0.1002392765347544</v>
       </c>
       <c r="T27">
-        <v>0.7406198039528861</v>
+        <v>0.7493771327158425</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.16</v>
       </c>
       <c r="W27">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.958966012777672</v>
+        <v>9.27164700686347</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08586146463571825</v>
+        <v>0.08578561077155179</v>
       </c>
       <c r="C28">
-        <v>16.75626647739942</v>
+        <v>16.5431785819982</v>
       </c>
       <c r="D28">
-        <v>19.73426647739942</v>
+        <v>19.7441785819982</v>
       </c>
       <c r="E28">
-        <v>5.798</v>
+        <v>6.021000000000001</v>
       </c>
       <c r="F28">
-        <v>5.798</v>
+        <v>6.021000000000001</v>
       </c>
       <c r="G28">
         <v>2.82</v>
@@ -3577,28 +3577,28 @@
         <v>2.876</v>
       </c>
       <c r="M28">
-        <v>0.310193</v>
+        <v>0.3221235000000001</v>
       </c>
       <c r="N28">
-        <v>2.565807</v>
+        <v>2.5538765</v>
       </c>
       <c r="O28">
-        <v>0.41052912</v>
+        <v>0.40862024</v>
       </c>
       <c r="P28">
-        <v>2.15527788</v>
+        <v>2.14525626</v>
       </c>
       <c r="Q28">
-        <v>2.92927788</v>
+        <v>2.91925626</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1002392765347544</v>
+        <v>0.1008928914678792</v>
       </c>
       <c r="T28">
-        <v>0.7493771327158425</v>
+        <v>0.7583743882942223</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.27164700686347</v>
+        <v>8.928252673275932</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08578561077155179</v>
+        <v>0.08570975690738532</v>
       </c>
       <c r="C29">
-        <v>16.5431785819982</v>
+        <v>16.33010064888175</v>
       </c>
       <c r="D29">
-        <v>19.7441785819982</v>
+        <v>19.75410064888175</v>
       </c>
       <c r="E29">
-        <v>6.021000000000001</v>
+        <v>6.244000000000001</v>
       </c>
       <c r="F29">
-        <v>6.021000000000001</v>
+        <v>6.244000000000001</v>
       </c>
       <c r="G29">
         <v>2.82</v>
@@ -3659,28 +3659,28 @@
         <v>2.876</v>
       </c>
       <c r="M29">
-        <v>0.3221235000000001</v>
+        <v>0.334054</v>
       </c>
       <c r="N29">
-        <v>2.5538765</v>
+        <v>2.541946</v>
       </c>
       <c r="O29">
-        <v>0.40862024</v>
+        <v>0.40671136</v>
       </c>
       <c r="P29">
-        <v>2.14525626</v>
+        <v>2.13523464</v>
       </c>
       <c r="Q29">
-        <v>2.91925626</v>
+        <v>2.90923464</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1008928914678792</v>
+        <v>0.1015646623713685</v>
       </c>
       <c r="T29">
-        <v>0.7583743882942223</v>
+        <v>0.7676215676386683</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.928252673275932</v>
+        <v>8.60938650637322</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08570975690738532</v>
+        <v>0.08563390304321883</v>
       </c>
       <c r="C30">
-        <v>16.33010064888175</v>
+        <v>16.11703269307669</v>
       </c>
       <c r="D30">
-        <v>19.75410064888175</v>
+        <v>19.7640326930767</v>
       </c>
       <c r="E30">
-        <v>6.244000000000001</v>
+        <v>6.467000000000001</v>
       </c>
       <c r="F30">
-        <v>6.244000000000001</v>
+        <v>6.467000000000001</v>
       </c>
       <c r="G30">
         <v>2.82</v>
@@ -3741,28 +3741,28 @@
         <v>2.876</v>
       </c>
       <c r="M30">
-        <v>0.334054</v>
+        <v>0.3459845000000001</v>
       </c>
       <c r="N30">
-        <v>2.541946</v>
+        <v>2.5300155</v>
       </c>
       <c r="O30">
-        <v>0.40671136</v>
+        <v>0.40480248</v>
       </c>
       <c r="P30">
-        <v>2.13523464</v>
+        <v>2.12521302</v>
       </c>
       <c r="Q30">
-        <v>2.90923464</v>
+        <v>2.89921302</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1015646623713685</v>
+        <v>0.1022553563988998</v>
       </c>
       <c r="T30">
-        <v>0.7676215676386683</v>
+        <v>0.77712923090831</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.60938650637322</v>
+        <v>8.312511109601729</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08563390304321883</v>
+        <v>0.08555804917905235</v>
       </c>
       <c r="C31">
-        <v>16.1170326930767</v>
+        <v>15.90397472963991</v>
       </c>
       <c r="D31">
-        <v>19.7640326930767</v>
+        <v>19.77397472963991</v>
       </c>
       <c r="E31">
-        <v>6.467</v>
+        <v>6.69</v>
       </c>
       <c r="F31">
-        <v>6.467</v>
+        <v>6.69</v>
       </c>
       <c r="G31">
         <v>2.82</v>
@@ -3823,28 +3823,28 @@
         <v>2.876</v>
       </c>
       <c r="M31">
-        <v>0.3459845</v>
+        <v>0.357915</v>
       </c>
       <c r="N31">
-        <v>2.5300155</v>
+        <v>2.518085</v>
       </c>
       <c r="O31">
-        <v>0.40480248</v>
+        <v>0.4028936</v>
       </c>
       <c r="P31">
-        <v>2.12521302</v>
+        <v>2.1151914</v>
       </c>
       <c r="Q31">
-        <v>2.89921302</v>
+        <v>2.8891914</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1022553563988998</v>
+        <v>0.1029657845415034</v>
       </c>
       <c r="T31">
-        <v>0.7771292309083099</v>
+        <v>0.7869085416999413</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.312511109601731</v>
+        <v>8.035427405948338</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08555804917905235</v>
+        <v>0.08548219531488588</v>
       </c>
       <c r="C32">
-        <v>15.90397472963991</v>
+        <v>15.69092677365856</v>
       </c>
       <c r="D32">
-        <v>19.77397472963991</v>
+        <v>19.78392677365856</v>
       </c>
       <c r="E32">
-        <v>6.69</v>
+        <v>6.913</v>
       </c>
       <c r="F32">
-        <v>6.69</v>
+        <v>6.913</v>
       </c>
       <c r="G32">
         <v>2.82</v>
@@ -3905,28 +3905,28 @@
         <v>2.876</v>
       </c>
       <c r="M32">
-        <v>0.357915</v>
+        <v>0.3698455</v>
       </c>
       <c r="N32">
-        <v>2.518085</v>
+        <v>2.5061545</v>
       </c>
       <c r="O32">
-        <v>0.4028936</v>
+        <v>0.40098472</v>
       </c>
       <c r="P32">
-        <v>2.1151914</v>
+        <v>2.10516978</v>
       </c>
       <c r="Q32">
-        <v>2.8891914</v>
+        <v>2.87916978</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1029657845415034</v>
+        <v>0.1036968048041824</v>
       </c>
       <c r="T32">
-        <v>0.7869085416999413</v>
+        <v>0.7969713107753882</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.035427405948338</v>
+        <v>7.776220070272587</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08548219531488588</v>
+        <v>0.0856213814507194</v>
       </c>
       <c r="C33">
-        <v>15.69092677365856</v>
+        <v>15.4496731878383</v>
       </c>
       <c r="D33">
-        <v>19.78392677365856</v>
+        <v>19.7656731878383</v>
       </c>
       <c r="E33">
-        <v>6.913</v>
+        <v>7.136</v>
       </c>
       <c r="F33">
-        <v>6.913</v>
+        <v>7.136</v>
       </c>
       <c r="G33">
         <v>2.82</v>
@@ -3987,45 +3987,45 @@
         <v>2.876</v>
       </c>
       <c r="M33">
-        <v>0.3698455</v>
+        <v>0.3874848</v>
       </c>
       <c r="N33">
-        <v>2.5061545</v>
+        <v>2.4885152</v>
       </c>
       <c r="O33">
-        <v>0.40098472</v>
+        <v>0.398162432</v>
       </c>
       <c r="P33">
-        <v>2.10516978</v>
+        <v>2.090352768</v>
       </c>
       <c r="Q33">
-        <v>2.87916978</v>
+        <v>2.864352768</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1036968048041824</v>
+        <v>0.1044493256628227</v>
       </c>
       <c r="T33">
-        <v>0.7969713107753882</v>
+        <v>0.8073300436471716</v>
       </c>
       <c r="U33">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.16</v>
       </c>
       <c r="W33">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.776220070272587</v>
+        <v>7.422226626696065</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0856213814507194</v>
+        <v>0.08555224758655293</v>
       </c>
       <c r="C34">
-        <v>15.4496731878383</v>
+        <v>15.23573554625424</v>
       </c>
       <c r="D34">
-        <v>19.7656731878383</v>
+        <v>19.77473554625424</v>
       </c>
       <c r="E34">
-        <v>7.136</v>
+        <v>7.359000000000001</v>
       </c>
       <c r="F34">
-        <v>7.136</v>
+        <v>7.359000000000001</v>
       </c>
       <c r="G34">
         <v>2.82</v>
@@ -4069,28 +4069,28 @@
         <v>2.876</v>
       </c>
       <c r="M34">
-        <v>0.3874848</v>
+        <v>0.3995937000000001</v>
       </c>
       <c r="N34">
-        <v>2.4885152</v>
+        <v>2.4764063</v>
       </c>
       <c r="O34">
-        <v>0.398162432</v>
+        <v>0.396225008</v>
       </c>
       <c r="P34">
-        <v>2.090352768</v>
+        <v>2.080181292</v>
       </c>
       <c r="Q34">
-        <v>2.864352768</v>
+        <v>2.854181292</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1044493256628227</v>
+        <v>0.105224309830676</v>
       </c>
       <c r="T34">
-        <v>0.8073300436471716</v>
+        <v>0.8179979924255756</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.422226626696065</v>
+        <v>7.197310668311336</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08555224758655293</v>
+        <v>0.08548311372238646</v>
       </c>
       <c r="C35">
-        <v>15.23573554625424</v>
+        <v>15.02180621847873</v>
       </c>
       <c r="D35">
-        <v>19.77473554625424</v>
+        <v>19.78380621847873</v>
       </c>
       <c r="E35">
-        <v>7.359000000000001</v>
+        <v>7.582000000000001</v>
       </c>
       <c r="F35">
-        <v>7.359000000000001</v>
+        <v>7.582000000000001</v>
       </c>
       <c r="G35">
         <v>2.82</v>
@@ -4151,28 +4151,28 @@
         <v>2.876</v>
       </c>
       <c r="M35">
-        <v>0.3995937000000001</v>
+        <v>0.4117026</v>
       </c>
       <c r="N35">
-        <v>2.4764063</v>
+        <v>2.4642974</v>
       </c>
       <c r="O35">
-        <v>0.396225008</v>
+        <v>0.394287584</v>
       </c>
       <c r="P35">
-        <v>2.080181292</v>
+        <v>2.070009816</v>
       </c>
       <c r="Q35">
-        <v>2.854181292</v>
+        <v>2.844009816</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.105224309830676</v>
+        <v>0.1060227783672522</v>
       </c>
       <c r="T35">
-        <v>0.8179979924255756</v>
+        <v>0.8289892123790827</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.197310668311336</v>
+        <v>6.985625060419827</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08548311372238646</v>
+        <v>0.08541397985821998</v>
       </c>
       <c r="C36">
-        <v>15.02180621847873</v>
+        <v>14.80788521595765</v>
       </c>
       <c r="D36">
-        <v>19.78380621847873</v>
+        <v>19.79288521595765</v>
       </c>
       <c r="E36">
-        <v>7.582000000000001</v>
+        <v>7.805000000000001</v>
       </c>
       <c r="F36">
-        <v>7.582000000000001</v>
+        <v>7.805000000000001</v>
       </c>
       <c r="G36">
         <v>2.82</v>
@@ -4233,28 +4233,28 @@
         <v>2.876</v>
       </c>
       <c r="M36">
-        <v>0.4117026</v>
+        <v>0.4238115000000001</v>
       </c>
       <c r="N36">
-        <v>2.4642974</v>
+        <v>2.4521885</v>
       </c>
       <c r="O36">
-        <v>0.394287584</v>
+        <v>0.3923501599999999</v>
       </c>
       <c r="P36">
-        <v>2.070009816</v>
+        <v>2.05983834</v>
       </c>
       <c r="Q36">
-        <v>2.844009816</v>
+        <v>2.83383834</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1060227783672522</v>
+        <v>0.1068458151664923</v>
       </c>
       <c r="T36">
-        <v>0.8289892123790827</v>
+        <v>0.8403186237157745</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.985625060419827</v>
+        <v>6.786035772979259</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08541397985821998</v>
+        <v>0.08534484599405351</v>
       </c>
       <c r="C37">
-        <v>14.80788521595765</v>
+        <v>14.59397255015792</v>
       </c>
       <c r="D37">
-        <v>19.79288521595765</v>
+        <v>19.80197255015792</v>
       </c>
       <c r="E37">
-        <v>7.805000000000001</v>
+        <v>8.028</v>
       </c>
       <c r="F37">
-        <v>7.805000000000001</v>
+        <v>8.028</v>
       </c>
       <c r="G37">
         <v>2.82</v>
@@ -4315,28 +4315,28 @@
         <v>2.876</v>
       </c>
       <c r="M37">
-        <v>0.4238115000000001</v>
+        <v>0.4359204</v>
       </c>
       <c r="N37">
-        <v>2.4521885</v>
+        <v>2.4400796</v>
       </c>
       <c r="O37">
-        <v>0.3923501599999999</v>
+        <v>0.390412736</v>
       </c>
       <c r="P37">
-        <v>2.05983834</v>
+        <v>2.049666864</v>
       </c>
       <c r="Q37">
-        <v>2.83383834</v>
+        <v>2.823666864</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1068458151664923</v>
+        <v>0.1076945718657086</v>
       </c>
       <c r="T37">
-        <v>0.8403186237157745</v>
+        <v>0.8520020791567381</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.786035772979259</v>
+        <v>6.597534779285391</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08534484599405351</v>
+        <v>0.08527571212988705</v>
       </c>
       <c r="C38">
-        <v>14.59397255015792</v>
+        <v>14.3800682325675</v>
       </c>
       <c r="D38">
-        <v>19.80197255015792</v>
+        <v>19.8110682325675</v>
       </c>
       <c r="E38">
-        <v>8.028</v>
+        <v>8.250999999999999</v>
       </c>
       <c r="F38">
-        <v>8.028</v>
+        <v>8.250999999999999</v>
       </c>
       <c r="G38">
         <v>2.82</v>
@@ -4397,28 +4397,28 @@
         <v>2.876</v>
       </c>
       <c r="M38">
-        <v>0.4359204</v>
+        <v>0.4480293</v>
       </c>
       <c r="N38">
-        <v>2.4400796</v>
+        <v>2.4279707</v>
       </c>
       <c r="O38">
-        <v>0.390412736</v>
+        <v>0.388475312</v>
       </c>
       <c r="P38">
-        <v>2.049666864</v>
+        <v>2.039495388</v>
       </c>
       <c r="Q38">
-        <v>2.823666864</v>
+        <v>2.813495388</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1076945718657086</v>
+        <v>0.1085702732220429</v>
       </c>
       <c r="T38">
-        <v>0.852002079156738</v>
+        <v>0.8640564379450337</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.597534779285391</v>
+        <v>6.419223028493896</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08527571212988705</v>
+        <v>0.08520657826572056</v>
       </c>
       <c r="C39">
-        <v>14.3800682325675</v>
+        <v>14.16617227469549</v>
       </c>
       <c r="D39">
-        <v>19.8110682325675</v>
+        <v>19.82017227469549</v>
       </c>
       <c r="E39">
-        <v>8.250999999999999</v>
+        <v>8.474</v>
       </c>
       <c r="F39">
-        <v>8.250999999999999</v>
+        <v>8.474</v>
       </c>
       <c r="G39">
         <v>2.82</v>
@@ -4479,28 +4479,28 @@
         <v>2.876</v>
       </c>
       <c r="M39">
-        <v>0.4480293</v>
+        <v>0.4601382</v>
       </c>
       <c r="N39">
-        <v>2.4279707</v>
+        <v>2.4158618</v>
       </c>
       <c r="O39">
-        <v>0.388475312</v>
+        <v>0.386537888</v>
       </c>
       <c r="P39">
-        <v>2.039495388</v>
+        <v>2.029323912</v>
       </c>
       <c r="Q39">
-        <v>2.813495388</v>
+        <v>2.803323912</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1085702732220429</v>
+        <v>0.1094742230092267</v>
       </c>
       <c r="T39">
-        <v>0.8640564379450337</v>
+        <v>0.8764996470168227</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.419223028493896</v>
+        <v>6.250296106691424</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08520657826572056</v>
+        <v>0.08546504440155409</v>
       </c>
       <c r="C40">
-        <v>14.16617227469549</v>
+        <v>13.90917836606828</v>
       </c>
       <c r="D40">
-        <v>19.82017227469549</v>
+        <v>19.78617836606828</v>
       </c>
       <c r="E40">
-        <v>8.474</v>
+        <v>8.697000000000001</v>
       </c>
       <c r="F40">
-        <v>8.474</v>
+        <v>8.697000000000001</v>
       </c>
       <c r="G40">
         <v>2.82</v>
@@ -4561,45 +4561,45 @@
         <v>2.876</v>
       </c>
       <c r="M40">
-        <v>0.4601382</v>
+        <v>0.4809441000000001</v>
       </c>
       <c r="N40">
-        <v>2.4158618</v>
+        <v>2.3950559</v>
       </c>
       <c r="O40">
-        <v>0.386537888</v>
+        <v>0.383208944</v>
       </c>
       <c r="P40">
-        <v>2.029323912</v>
+        <v>2.011846956</v>
       </c>
       <c r="Q40">
-        <v>2.803323912</v>
+        <v>2.785846956</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1094742230092267</v>
+        <v>0.110407810494351</v>
       </c>
       <c r="T40">
-        <v>0.8764996470168227</v>
+        <v>0.8893508301565393</v>
       </c>
       <c r="U40">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.16</v>
       </c>
       <c r="W40">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>6.250296106691424</v>
+        <v>5.97990494113557</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08546504440155409</v>
+        <v>0.08540431053738762</v>
       </c>
       <c r="C41">
-        <v>13.90917836606828</v>
+        <v>13.69415570278546</v>
       </c>
       <c r="D41">
-        <v>19.78617836606828</v>
+        <v>19.79415570278546</v>
       </c>
       <c r="E41">
-        <v>8.697000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="F41">
-        <v>8.697000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="G41">
         <v>2.82</v>
@@ -4643,28 +4643,28 @@
         <v>2.876</v>
       </c>
       <c r="M41">
-        <v>0.4809441000000001</v>
+        <v>0.493276</v>
       </c>
       <c r="N41">
-        <v>2.3950559</v>
+        <v>2.382724</v>
       </c>
       <c r="O41">
-        <v>0.383208944</v>
+        <v>0.38123584</v>
       </c>
       <c r="P41">
-        <v>2.011846956</v>
+        <v>2.00148816</v>
       </c>
       <c r="Q41">
-        <v>2.785846956</v>
+        <v>2.77548816</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.110407810494351</v>
+        <v>0.1113725175623127</v>
       </c>
       <c r="T41">
-        <v>0.8893508301565393</v>
+        <v>0.9026303860675798</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.97990494113557</v>
+        <v>5.830407317607182</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08540431053738762</v>
+        <v>0.08534357667322114</v>
       </c>
       <c r="C42">
-        <v>13.69415570278546</v>
+        <v>13.47913947465831</v>
       </c>
       <c r="D42">
-        <v>19.79415570278546</v>
+        <v>19.80213947465831</v>
       </c>
       <c r="E42">
-        <v>8.92</v>
+        <v>9.143000000000001</v>
       </c>
       <c r="F42">
-        <v>8.92</v>
+        <v>9.143000000000001</v>
       </c>
       <c r="G42">
         <v>2.82</v>
@@ -4725,28 +4725,28 @@
         <v>2.876</v>
       </c>
       <c r="M42">
-        <v>0.493276</v>
+        <v>0.5056079000000001</v>
       </c>
       <c r="N42">
-        <v>2.382724</v>
+        <v>2.3703921</v>
       </c>
       <c r="O42">
-        <v>0.38123584</v>
+        <v>0.3792627359999999</v>
       </c>
       <c r="P42">
-        <v>2.00148816</v>
+        <v>1.991129364</v>
       </c>
       <c r="Q42">
-        <v>2.77548816</v>
+        <v>2.765129364</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1113725175623127</v>
+        <v>0.1123699265647816</v>
       </c>
       <c r="T42">
-        <v>0.9026303860675798</v>
+        <v>0.9163600964162826</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.830407317607182</v>
+        <v>5.688202261080176</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08534357667322114</v>
+        <v>0.08528284280905467</v>
       </c>
       <c r="C43">
-        <v>13.47913947465831</v>
+        <v>13.26412968947661</v>
       </c>
       <c r="D43">
-        <v>19.80213947465831</v>
+        <v>19.81012968947661</v>
       </c>
       <c r="E43">
-        <v>9.143000000000001</v>
+        <v>9.366000000000001</v>
       </c>
       <c r="F43">
-        <v>9.143000000000001</v>
+        <v>9.366000000000001</v>
       </c>
       <c r="G43">
         <v>2.82</v>
@@ -4807,28 +4807,28 @@
         <v>2.876</v>
       </c>
       <c r="M43">
-        <v>0.5056079000000001</v>
+        <v>0.5179398000000001</v>
       </c>
       <c r="N43">
-        <v>2.3703921</v>
+        <v>2.3580602</v>
       </c>
       <c r="O43">
-        <v>0.3792627359999999</v>
+        <v>0.377289632</v>
       </c>
       <c r="P43">
-        <v>1.991129364</v>
+        <v>1.980770568</v>
       </c>
       <c r="Q43">
-        <v>2.765129364</v>
+        <v>2.754770568</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1123699265647816</v>
+        <v>0.1134017289811287</v>
       </c>
       <c r="T43">
-        <v>0.9163600964162826</v>
+        <v>0.9305632450528718</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.688202261080176</v>
+        <v>5.5527688739116</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08528284280905468</v>
+        <v>0.0852221089448882</v>
       </c>
       <c r="C44">
-        <v>13.2641296894766</v>
+        <v>13.04912635504275</v>
       </c>
       <c r="D44">
-        <v>19.8101296894766</v>
+        <v>19.81812635504275</v>
       </c>
       <c r="E44">
-        <v>9.366</v>
+        <v>9.589</v>
       </c>
       <c r="F44">
-        <v>9.366</v>
+        <v>9.589</v>
       </c>
       <c r="G44">
         <v>2.82</v>
@@ -4889,28 +4889,28 @@
         <v>2.876</v>
       </c>
       <c r="M44">
-        <v>0.5179398</v>
+        <v>0.5302717</v>
       </c>
       <c r="N44">
-        <v>2.3580602</v>
+        <v>2.3457283</v>
       </c>
       <c r="O44">
-        <v>0.377289632</v>
+        <v>0.375316528</v>
       </c>
       <c r="P44">
-        <v>1.980770568</v>
+        <v>1.970411772</v>
       </c>
       <c r="Q44">
-        <v>2.754770568</v>
+        <v>2.744411772</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1134017289811287</v>
+        <v>0.1144697349910319</v>
       </c>
       <c r="T44">
-        <v>0.9305632450528718</v>
+        <v>0.9452647497819728</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.552768873911601</v>
+        <v>5.423634714053192</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0852221089448882</v>
+        <v>0.08516137508072172</v>
       </c>
       <c r="C45">
-        <v>13.04912635504275</v>
+        <v>12.83412947917173</v>
       </c>
       <c r="D45">
-        <v>19.81812635504275</v>
+        <v>19.82612947917173</v>
       </c>
       <c r="E45">
-        <v>9.589</v>
+        <v>9.812000000000001</v>
       </c>
       <c r="F45">
-        <v>9.589</v>
+        <v>9.812000000000001</v>
       </c>
       <c r="G45">
         <v>2.82</v>
@@ -4971,28 +4971,28 @@
         <v>2.876</v>
       </c>
       <c r="M45">
-        <v>0.5302717</v>
+        <v>0.5426036000000001</v>
       </c>
       <c r="N45">
-        <v>2.3457283</v>
+        <v>2.3333964</v>
       </c>
       <c r="O45">
-        <v>0.375316528</v>
+        <v>0.373343424</v>
       </c>
       <c r="P45">
-        <v>1.970411772</v>
+        <v>1.960052976</v>
       </c>
       <c r="Q45">
-        <v>2.744411772</v>
+        <v>2.734052976</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1144697349910319</v>
+        <v>0.1155758840727173</v>
       </c>
       <c r="T45">
-        <v>0.9452647497819728</v>
+        <v>0.9604913082513989</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.423634714053192</v>
+        <v>5.3003702887338</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08516137508072172</v>
+        <v>0.08510064121655525</v>
       </c>
       <c r="C46">
-        <v>12.83412947917173</v>
+        <v>12.61913906969116</v>
       </c>
       <c r="D46">
-        <v>19.82612947917173</v>
+        <v>19.83413906969116</v>
       </c>
       <c r="E46">
-        <v>9.812000000000001</v>
+        <v>10.035</v>
       </c>
       <c r="F46">
-        <v>9.812000000000001</v>
+        <v>10.035</v>
       </c>
       <c r="G46">
         <v>2.82</v>
@@ -5053,28 +5053,28 @@
         <v>2.876</v>
       </c>
       <c r="M46">
-        <v>0.5426036000000001</v>
+        <v>0.5549355</v>
       </c>
       <c r="N46">
-        <v>2.3333964</v>
+        <v>2.3210645</v>
       </c>
       <c r="O46">
-        <v>0.373343424</v>
+        <v>0.37137032</v>
       </c>
       <c r="P46">
-        <v>1.960052976</v>
+        <v>1.94969418</v>
       </c>
       <c r="Q46">
-        <v>2.734052976</v>
+        <v>2.72369418</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1155758840727173</v>
+        <v>0.1167222567573732</v>
       </c>
       <c r="T46">
-        <v>0.9604913082513989</v>
+        <v>0.9762715597560768</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.3003702887338</v>
+        <v>5.182584282317494</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08510064121655525</v>
+        <v>0.08503990735238875</v>
       </c>
       <c r="C47">
-        <v>12.61913906969116</v>
+        <v>12.40415513444131</v>
       </c>
       <c r="D47">
-        <v>19.83413906969116</v>
+        <v>19.84215513444131</v>
       </c>
       <c r="E47">
-        <v>10.035</v>
+        <v>10.258</v>
       </c>
       <c r="F47">
-        <v>10.035</v>
+        <v>10.258</v>
       </c>
       <c r="G47">
         <v>2.82</v>
@@ -5135,28 +5135,28 @@
         <v>2.876</v>
       </c>
       <c r="M47">
-        <v>0.5549355</v>
+        <v>0.5672674000000001</v>
       </c>
       <c r="N47">
-        <v>2.3210645</v>
+        <v>2.3087326</v>
       </c>
       <c r="O47">
-        <v>0.37137032</v>
+        <v>0.369397216</v>
       </c>
       <c r="P47">
-        <v>1.94969418</v>
+        <v>1.939335384</v>
       </c>
       <c r="Q47">
-        <v>2.72369418</v>
+        <v>2.713335384</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1167222567573732</v>
+        <v>0.1179110876896088</v>
       </c>
       <c r="T47">
-        <v>0.9762715597560768</v>
+        <v>0.9926362650201874</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.182584282317494</v>
+        <v>5.06991940661494</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08503990735238875</v>
+        <v>0.08497917348822229</v>
       </c>
       <c r="C48">
-        <v>12.40415513444131</v>
+        <v>12.18917768127513</v>
       </c>
       <c r="D48">
-        <v>19.84215513444131</v>
+        <v>19.85017768127513</v>
       </c>
       <c r="E48">
-        <v>10.258</v>
+        <v>10.481</v>
       </c>
       <c r="F48">
-        <v>10.258</v>
+        <v>10.481</v>
       </c>
       <c r="G48">
         <v>2.82</v>
@@ -5217,28 +5217,28 @@
         <v>2.876</v>
       </c>
       <c r="M48">
-        <v>0.5672674000000001</v>
+        <v>0.5795993000000002</v>
       </c>
       <c r="N48">
-        <v>2.3087326</v>
+        <v>2.2964007</v>
       </c>
       <c r="O48">
-        <v>0.369397216</v>
+        <v>0.3674241119999999</v>
       </c>
       <c r="P48">
-        <v>1.939335384</v>
+        <v>1.928976588</v>
       </c>
       <c r="Q48">
-        <v>2.713335384</v>
+        <v>2.702976587999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1179110876896088</v>
+        <v>0.1191447801664572</v>
       </c>
       <c r="T48">
-        <v>0.9926362650201874</v>
+        <v>1.009618506332</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.06991940661494</v>
+        <v>4.96204878094228</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08497917348822229</v>
+        <v>0.08491843962405582</v>
       </c>
       <c r="C49">
-        <v>12.18917768127513</v>
+        <v>11.97420671805826</v>
       </c>
       <c r="D49">
-        <v>19.85017768127513</v>
+        <v>19.85820671805826</v>
       </c>
       <c r="E49">
-        <v>10.481</v>
+        <v>10.704</v>
       </c>
       <c r="F49">
-        <v>10.481</v>
+        <v>10.704</v>
       </c>
       <c r="G49">
         <v>2.82</v>
@@ -5299,28 +5299,28 @@
         <v>2.876</v>
       </c>
       <c r="M49">
-        <v>0.5795993000000002</v>
+        <v>0.5919312000000001</v>
       </c>
       <c r="N49">
-        <v>2.2964007</v>
+        <v>2.2840688</v>
       </c>
       <c r="O49">
-        <v>0.3674241119999999</v>
+        <v>0.365451008</v>
       </c>
       <c r="P49">
-        <v>1.928976588</v>
+        <v>1.918617792</v>
       </c>
       <c r="Q49">
-        <v>2.702976587999999</v>
+        <v>2.692617792</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1191447801664572</v>
+        <v>0.1204259223539535</v>
       </c>
       <c r="T49">
-        <v>1.009618506332</v>
+        <v>1.02725391077119</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.96204878094228</v>
+        <v>4.858672764672651</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08491843962405582</v>
+        <v>0.08485770575988935</v>
       </c>
       <c r="C50">
-        <v>11.97420671805826</v>
+        <v>11.75924225266912</v>
       </c>
       <c r="D50">
-        <v>19.85820671805826</v>
+        <v>19.86624225266912</v>
       </c>
       <c r="E50">
-        <v>10.704</v>
+        <v>10.927</v>
       </c>
       <c r="F50">
-        <v>10.704</v>
+        <v>10.927</v>
       </c>
       <c r="G50">
         <v>2.82</v>
@@ -5381,28 +5381,28 @@
         <v>2.876</v>
       </c>
       <c r="M50">
-        <v>0.5919312000000001</v>
+        <v>0.6042631000000001</v>
       </c>
       <c r="N50">
-        <v>2.2840688</v>
+        <v>2.2717369</v>
       </c>
       <c r="O50">
-        <v>0.365451008</v>
+        <v>0.363477904</v>
       </c>
       <c r="P50">
-        <v>1.918617792</v>
+        <v>1.908258996</v>
       </c>
       <c r="Q50">
-        <v>2.692617792</v>
+        <v>2.682258996</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1204259223539535</v>
+        <v>0.1217573054115478</v>
       </c>
       <c r="T50">
-        <v>1.02725391077119</v>
+        <v>1.045580899698192</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.858672764672651</v>
+        <v>4.759516177638515</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08485770575988935</v>
+        <v>0.08479697189572286</v>
       </c>
       <c r="C51">
-        <v>11.75924225266912</v>
+        <v>11.54428429299883</v>
       </c>
       <c r="D51">
-        <v>19.86624225266912</v>
+        <v>19.87428429299883</v>
       </c>
       <c r="E51">
-        <v>10.927</v>
+        <v>11.15</v>
       </c>
       <c r="F51">
-        <v>10.927</v>
+        <v>11.15</v>
       </c>
       <c r="G51">
         <v>2.82</v>
@@ -5463,28 +5463,28 @@
         <v>2.876</v>
       </c>
       <c r="M51">
-        <v>0.6042631000000001</v>
+        <v>0.616595</v>
       </c>
       <c r="N51">
-        <v>2.2717369</v>
+        <v>2.259405</v>
       </c>
       <c r="O51">
-        <v>0.363477904</v>
+        <v>0.3615048</v>
       </c>
       <c r="P51">
-        <v>1.908258996</v>
+        <v>1.8979002</v>
       </c>
       <c r="Q51">
-        <v>2.682258996</v>
+        <v>2.6719002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1217573054115478</v>
+        <v>0.1231419437914457</v>
       </c>
       <c r="T51">
-        <v>1.045580899698192</v>
+        <v>1.064640968182273</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.759516177638515</v>
+        <v>4.664325854085745</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08479697189572286</v>
+        <v>0.08473623803155639</v>
       </c>
       <c r="C52">
-        <v>11.54428429299883</v>
+        <v>11.32933284695132</v>
       </c>
       <c r="D52">
-        <v>19.87428429299883</v>
+        <v>19.88233284695132</v>
       </c>
       <c r="E52">
-        <v>11.15</v>
+        <v>11.373</v>
       </c>
       <c r="F52">
-        <v>11.15</v>
+        <v>11.373</v>
       </c>
       <c r="G52">
         <v>2.82</v>
@@ -5545,28 +5545,28 @@
         <v>2.876</v>
       </c>
       <c r="M52">
-        <v>0.616595</v>
+        <v>0.6289269000000001</v>
       </c>
       <c r="N52">
-        <v>2.259405</v>
+        <v>2.2470731</v>
       </c>
       <c r="O52">
-        <v>0.3615048</v>
+        <v>0.359531696</v>
       </c>
       <c r="P52">
-        <v>1.8979002</v>
+        <v>1.887541404</v>
       </c>
       <c r="Q52">
-        <v>2.6719002</v>
+        <v>2.661541404</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1231419437914457</v>
+        <v>0.1245830980235845</v>
       </c>
       <c r="T52">
-        <v>1.064640968182273</v>
+        <v>1.084478998645297</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.664325854085745</v>
+        <v>4.572868484397788</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08473623803155639</v>
+        <v>0.08576750416738992</v>
       </c>
       <c r="C53">
-        <v>11.32933284695132</v>
+        <v>10.97054611111847</v>
       </c>
       <c r="D53">
-        <v>19.88233284695132</v>
+        <v>19.74654611111847</v>
       </c>
       <c r="E53">
-        <v>11.373</v>
+        <v>11.596</v>
       </c>
       <c r="F53">
-        <v>11.373</v>
+        <v>11.596</v>
       </c>
       <c r="G53">
         <v>2.82</v>
@@ -5627,45 +5627,45 @@
         <v>2.876</v>
       </c>
       <c r="M53">
-        <v>0.6289269000000001</v>
+        <v>0.6702488000000001</v>
       </c>
       <c r="N53">
-        <v>2.2470731</v>
+        <v>2.2057512</v>
       </c>
       <c r="O53">
-        <v>0.359531696</v>
+        <v>0.352920192</v>
       </c>
       <c r="P53">
-        <v>1.887541404</v>
+        <v>1.852831008</v>
       </c>
       <c r="Q53">
-        <v>2.661541404</v>
+        <v>2.626831008</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1245830980235845</v>
+        <v>0.126084300348729</v>
       </c>
       <c r="T53">
-        <v>1.084478998645297</v>
+        <v>1.105143613710947</v>
       </c>
       <c r="U53">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V53">
         <v>0.16</v>
       </c>
       <c r="W53">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.572868484397788</v>
+        <v>4.290943900235256</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08576750416738992</v>
+        <v>0.08572777030322346</v>
       </c>
       <c r="C54">
-        <v>10.97054611111847</v>
+        <v>10.75274350333397</v>
       </c>
       <c r="D54">
-        <v>19.74654611111847</v>
+        <v>19.75174350333397</v>
       </c>
       <c r="E54">
-        <v>11.596</v>
+        <v>11.819</v>
       </c>
       <c r="F54">
-        <v>11.596</v>
+        <v>11.819</v>
       </c>
       <c r="G54">
         <v>2.82</v>
@@ -5709,28 +5709,28 @@
         <v>2.876</v>
       </c>
       <c r="M54">
-        <v>0.6702488000000001</v>
+        <v>0.6831382000000001</v>
       </c>
       <c r="N54">
-        <v>2.2057512</v>
+        <v>2.1928618</v>
       </c>
       <c r="O54">
-        <v>0.352920192</v>
+        <v>0.350857888</v>
       </c>
       <c r="P54">
-        <v>1.852831008</v>
+        <v>1.842003912</v>
       </c>
       <c r="Q54">
-        <v>2.626831008</v>
+        <v>2.616003912</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.126084300348729</v>
+        <v>0.1276493836238797</v>
       </c>
       <c r="T54">
-        <v>1.105143613710947</v>
+        <v>1.126687574098539</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.290943900235256</v>
+        <v>4.209982694570439</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08572777030322346</v>
+        <v>0.08568803643905697</v>
       </c>
       <c r="C55">
-        <v>10.75274350333397</v>
+        <v>10.53494363223037</v>
       </c>
       <c r="D55">
-        <v>19.75174350333397</v>
+        <v>19.75694363223037</v>
       </c>
       <c r="E55">
-        <v>11.819</v>
+        <v>12.042</v>
       </c>
       <c r="F55">
-        <v>11.819</v>
+        <v>12.042</v>
       </c>
       <c r="G55">
         <v>2.82</v>
@@ -5791,28 +5791,28 @@
         <v>2.876</v>
       </c>
       <c r="M55">
-        <v>0.6831382000000001</v>
+        <v>0.6960276000000002</v>
       </c>
       <c r="N55">
-        <v>2.1928618</v>
+        <v>2.1799724</v>
       </c>
       <c r="O55">
-        <v>0.350857888</v>
+        <v>0.3487955839999999</v>
       </c>
       <c r="P55">
-        <v>1.842003912</v>
+        <v>1.831176816</v>
       </c>
       <c r="Q55">
-        <v>2.616003912</v>
+        <v>2.605176816</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1276493836238797</v>
+        <v>0.1292825139979499</v>
       </c>
       <c r="T55">
-        <v>1.126687574098539</v>
+        <v>1.149168228416027</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.209982694570439</v>
+        <v>4.132020052078393</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08568803643905697</v>
+        <v>0.08564830257489051</v>
       </c>
       <c r="C56">
-        <v>10.53494363223037</v>
+        <v>10.31714649996971</v>
       </c>
       <c r="D56">
-        <v>19.75694363223037</v>
+        <v>19.76214649996971</v>
       </c>
       <c r="E56">
-        <v>12.042</v>
+        <v>12.265</v>
       </c>
       <c r="F56">
-        <v>12.042</v>
+        <v>12.265</v>
       </c>
       <c r="G56">
         <v>2.82</v>
@@ -5873,28 +5873,28 @@
         <v>2.876</v>
       </c>
       <c r="M56">
-        <v>0.6960276000000002</v>
+        <v>0.7089170000000001</v>
       </c>
       <c r="N56">
-        <v>2.1799724</v>
+        <v>2.167083</v>
       </c>
       <c r="O56">
-        <v>0.3487955839999999</v>
+        <v>0.34673328</v>
       </c>
       <c r="P56">
-        <v>1.831176816</v>
+        <v>1.82034972</v>
       </c>
       <c r="Q56">
-        <v>2.605176816</v>
+        <v>2.59434972</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1292825139979499</v>
+        <v>0.1309882279442011</v>
       </c>
       <c r="T56">
-        <v>1.149168228416027</v>
+        <v>1.172648022925403</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.132020052078393</v>
+        <v>4.056892414767878</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08564830257489051</v>
+        <v>0.08725496871072402</v>
       </c>
       <c r="C57">
-        <v>10.31714649996971</v>
+        <v>9.885926785221903</v>
       </c>
       <c r="D57">
-        <v>19.76214649996971</v>
+        <v>19.5539267852219</v>
       </c>
       <c r="E57">
-        <v>12.265</v>
+        <v>12.488</v>
       </c>
       <c r="F57">
-        <v>12.265</v>
+        <v>12.488</v>
       </c>
       <c r="G57">
         <v>2.82</v>
@@ -5955,45 +5955,45 @@
         <v>2.876</v>
       </c>
       <c r="M57">
-        <v>0.7089170000000001</v>
+        <v>0.7655144</v>
       </c>
       <c r="N57">
-        <v>2.167083</v>
+        <v>2.1104856</v>
       </c>
       <c r="O57">
-        <v>0.34673328</v>
+        <v>0.337677696</v>
       </c>
       <c r="P57">
-        <v>1.82034972</v>
+        <v>1.772807904</v>
       </c>
       <c r="Q57">
-        <v>2.59434972</v>
+        <v>2.546807904</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1309882279442011</v>
+        <v>0.1327714743425546</v>
       </c>
       <c r="T57">
-        <v>1.172648022925403</v>
+        <v>1.197195080821569</v>
       </c>
       <c r="U57">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V57">
         <v>0.16</v>
       </c>
       <c r="W57">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.056892414767878</v>
+        <v>3.756950881655524</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08725496871072402</v>
+        <v>0.08724463484655755</v>
       </c>
       <c r="C58">
-        <v>9.885926785221903</v>
+        <v>9.664252006066555</v>
       </c>
       <c r="D58">
-        <v>19.5539267852219</v>
+        <v>19.55525200606656</v>
       </c>
       <c r="E58">
-        <v>12.488</v>
+        <v>12.711</v>
       </c>
       <c r="F58">
-        <v>12.488</v>
+        <v>12.711</v>
       </c>
       <c r="G58">
         <v>2.82</v>
@@ -6037,28 +6037,28 @@
         <v>2.876</v>
       </c>
       <c r="M58">
-        <v>0.7655144</v>
+        <v>0.7791843000000002</v>
       </c>
       <c r="N58">
-        <v>2.1104856</v>
+        <v>2.0968157</v>
       </c>
       <c r="O58">
-        <v>0.337677696</v>
+        <v>0.335490512</v>
       </c>
       <c r="P58">
-        <v>1.772807904</v>
+        <v>1.761325188</v>
       </c>
       <c r="Q58">
-        <v>2.546807904</v>
+        <v>2.535325188</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1327714743425546</v>
+        <v>0.1346376624338548</v>
       </c>
       <c r="T58">
-        <v>1.197195080821569</v>
+        <v>1.222883862340812</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.756950881655524</v>
+        <v>3.691039462679111</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08724463484655755</v>
+        <v>0.08723430098239107</v>
       </c>
       <c r="C59">
-        <v>9.664252006066555</v>
+        <v>9.442577406550756</v>
       </c>
       <c r="D59">
-        <v>19.55525200606656</v>
+        <v>19.55657740655076</v>
       </c>
       <c r="E59">
-        <v>12.711</v>
+        <v>12.934</v>
       </c>
       <c r="F59">
-        <v>12.711</v>
+        <v>12.934</v>
       </c>
       <c r="G59">
         <v>2.82</v>
@@ -6119,28 +6119,28 @@
         <v>2.876</v>
       </c>
       <c r="M59">
-        <v>0.7791843000000002</v>
+        <v>0.7928542000000002</v>
       </c>
       <c r="N59">
-        <v>2.0968157</v>
+        <v>2.0831458</v>
       </c>
       <c r="O59">
-        <v>0.335490512</v>
+        <v>0.333303328</v>
       </c>
       <c r="P59">
-        <v>1.761325188</v>
+        <v>1.749842472</v>
       </c>
       <c r="Q59">
-        <v>2.535325188</v>
+        <v>2.523842472</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1346376624338548</v>
+        <v>0.1365927166247407</v>
       </c>
       <c r="T59">
-        <v>1.222883862340812</v>
+        <v>1.249795919170495</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.691039462679111</v>
+        <v>3.627400851253609</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08723430098239107</v>
+        <v>0.0872239671182246</v>
       </c>
       <c r="C60">
-        <v>9.442577406550759</v>
+        <v>9.220902986711039</v>
       </c>
       <c r="D60">
-        <v>19.55657740655076</v>
+        <v>19.55790298671104</v>
       </c>
       <c r="E60">
-        <v>12.934</v>
+        <v>13.157</v>
       </c>
       <c r="F60">
-        <v>12.934</v>
+        <v>13.157</v>
       </c>
       <c r="G60">
         <v>2.82</v>
@@ -6201,28 +6201,28 @@
         <v>2.876</v>
       </c>
       <c r="M60">
-        <v>0.7928542</v>
+        <v>0.8065241</v>
       </c>
       <c r="N60">
-        <v>2.0831458</v>
+        <v>2.0694759</v>
       </c>
       <c r="O60">
-        <v>0.333303328</v>
+        <v>0.331116144</v>
       </c>
       <c r="P60">
-        <v>1.749842472</v>
+        <v>1.738359756</v>
       </c>
       <c r="Q60">
-        <v>2.523842472</v>
+        <v>2.512359756</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1365927166247407</v>
+        <v>0.1386431393127429</v>
       </c>
       <c r="T60">
-        <v>1.249795919170495</v>
+        <v>1.278020759260163</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.62740085125361</v>
+        <v>3.565919480893379</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.0872239671182246</v>
+        <v>0.08721363325405812</v>
       </c>
       <c r="C61">
-        <v>9.220902986711039</v>
+        <v>8.99922874658394</v>
       </c>
       <c r="D61">
-        <v>19.55790298671104</v>
+        <v>19.55922874658394</v>
       </c>
       <c r="E61">
-        <v>13.157</v>
+        <v>13.38</v>
       </c>
       <c r="F61">
-        <v>13.157</v>
+        <v>13.38</v>
       </c>
       <c r="G61">
         <v>2.82</v>
@@ -6283,28 +6283,28 @@
         <v>2.876</v>
       </c>
       <c r="M61">
-        <v>0.8065241</v>
+        <v>0.8201940000000001</v>
       </c>
       <c r="N61">
-        <v>2.0694759</v>
+        <v>2.055806</v>
       </c>
       <c r="O61">
-        <v>0.331116144</v>
+        <v>0.3289289599999999</v>
       </c>
       <c r="P61">
-        <v>1.738359756</v>
+        <v>1.72687704</v>
       </c>
       <c r="Q61">
-        <v>2.512359756</v>
+        <v>2.50087704</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1386431393127429</v>
+        <v>0.1407960831351453</v>
       </c>
       <c r="T61">
-        <v>1.278020759260163</v>
+        <v>1.307656841354314</v>
       </c>
       <c r="U61">
         <v>0.0613</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.565919480893379</v>
+        <v>3.506487489545155</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08721363325405812</v>
+        <v>0.08863801938989166</v>
       </c>
       <c r="C62">
-        <v>8.99922874658394</v>
+        <v>8.59516965981633</v>
       </c>
       <c r="D62">
-        <v>19.55922874658394</v>
+        <v>19.37816965981633</v>
       </c>
       <c r="E62">
-        <v>13.38</v>
+        <v>13.603</v>
       </c>
       <c r="F62">
-        <v>13.38</v>
+        <v>13.603</v>
       </c>
       <c r="G62">
         <v>2.82</v>
@@ -6365,45 +6365,45 @@
         <v>2.876</v>
       </c>
       <c r="M62">
-        <v>0.8201940000000001</v>
+        <v>0.8719523</v>
       </c>
       <c r="N62">
-        <v>2.055806</v>
+        <v>2.0040477</v>
       </c>
       <c r="O62">
-        <v>0.3289289599999999</v>
+        <v>0.320647632</v>
       </c>
       <c r="P62">
-        <v>1.72687704</v>
+        <v>1.683400068</v>
       </c>
       <c r="Q62">
-        <v>2.50087704</v>
+        <v>2.457400068</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1407960831351453</v>
+        <v>0.1430594343330555</v>
       </c>
       <c r="T62">
-        <v>1.307656841354314</v>
+        <v>1.338812722530217</v>
       </c>
       <c r="U62">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V62">
         <v>0.16</v>
       </c>
       <c r="W62">
-        <v>0.051492</v>
+        <v>0.053844</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.506487489545155</v>
+        <v>3.298345563168994</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08863801938989166</v>
+        <v>0.08865120552572517</v>
       </c>
       <c r="C63">
-        <v>8.59516965981633</v>
+        <v>8.370509178682898</v>
       </c>
       <c r="D63">
-        <v>19.37816965981633</v>
+        <v>19.3765091786829</v>
       </c>
       <c r="E63">
-        <v>13.603</v>
+        <v>13.826</v>
       </c>
       <c r="F63">
-        <v>13.603</v>
+        <v>13.826</v>
       </c>
       <c r="G63">
         <v>2.82</v>
@@ -6447,28 +6447,28 @@
         <v>2.876</v>
       </c>
       <c r="M63">
-        <v>0.8719523</v>
+        <v>0.8862466000000001</v>
       </c>
       <c r="N63">
-        <v>2.0040477</v>
+        <v>1.9897534</v>
       </c>
       <c r="O63">
-        <v>0.320647632</v>
+        <v>0.318360544</v>
       </c>
       <c r="P63">
-        <v>1.683400068</v>
+        <v>1.671392856</v>
       </c>
       <c r="Q63">
-        <v>2.457400068</v>
+        <v>2.445392856</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1430594343330555</v>
+        <v>0.1454419092782241</v>
       </c>
       <c r="T63">
-        <v>1.338812722530217</v>
+        <v>1.371608386925904</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.298345563168994</v>
+        <v>3.245146441182397</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08865120552572517</v>
+        <v>0.08866439166155871</v>
       </c>
       <c r="C64">
-        <v>8.370509178682898</v>
+        <v>8.145848982092469</v>
       </c>
       <c r="D64">
-        <v>19.3765091786829</v>
+        <v>19.37484898209247</v>
       </c>
       <c r="E64">
-        <v>13.826</v>
+        <v>14.049</v>
       </c>
       <c r="F64">
-        <v>13.826</v>
+        <v>14.049</v>
       </c>
       <c r="G64">
         <v>2.82</v>
@@ -6529,28 +6529,28 @@
         <v>2.876</v>
       </c>
       <c r="M64">
-        <v>0.8862466000000001</v>
+        <v>0.9005409000000001</v>
       </c>
       <c r="N64">
-        <v>1.9897534</v>
+        <v>1.9754591</v>
       </c>
       <c r="O64">
-        <v>0.318360544</v>
+        <v>0.316073456</v>
       </c>
       <c r="P64">
-        <v>1.671392856</v>
+        <v>1.659385644</v>
       </c>
       <c r="Q64">
-        <v>2.445392856</v>
+        <v>2.433385643999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1454419092782241</v>
+        <v>0.1479531666528613</v>
       </c>
       <c r="T64">
-        <v>1.371608386925904</v>
+        <v>1.406176789937574</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.245146441182397</v>
+        <v>3.193636180211248</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.08866439166155871</v>
+        <v>0.08867757779739222</v>
       </c>
       <c r="C65">
-        <v>8.145848982092469</v>
+        <v>7.921189069971925</v>
       </c>
       <c r="D65">
-        <v>19.37484898209247</v>
+        <v>19.37318906997193</v>
       </c>
       <c r="E65">
-        <v>14.049</v>
+        <v>14.272</v>
       </c>
       <c r="F65">
-        <v>14.049</v>
+        <v>14.272</v>
       </c>
       <c r="G65">
         <v>2.82</v>
@@ -6611,28 +6611,28 @@
         <v>2.876</v>
       </c>
       <c r="M65">
-        <v>0.9005409000000001</v>
+        <v>0.9148352000000001</v>
       </c>
       <c r="N65">
-        <v>1.9754591</v>
+        <v>1.9611648</v>
       </c>
       <c r="O65">
-        <v>0.316073456</v>
+        <v>0.313786368</v>
       </c>
       <c r="P65">
-        <v>1.659385644</v>
+        <v>1.647378432</v>
       </c>
       <c r="Q65">
-        <v>2.433385643999999</v>
+        <v>2.421378432</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1479531666528613</v>
+        <v>0.1506039383260895</v>
       </c>
       <c r="T65">
-        <v>1.406176789937574</v>
+        <v>1.442665659783226</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.193636180211248</v>
+        <v>3.143735614895447</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.08867757779739222</v>
+        <v>0.08869076393322575</v>
       </c>
       <c r="C66">
-        <v>7.921189069971925</v>
+        <v>7.696529442248142</v>
       </c>
       <c r="D66">
-        <v>19.37318906997193</v>
+        <v>19.37152944224814</v>
       </c>
       <c r="E66">
-        <v>14.272</v>
+        <v>14.495</v>
       </c>
       <c r="F66">
-        <v>14.272</v>
+        <v>14.495</v>
       </c>
       <c r="G66">
         <v>2.82</v>
@@ -6693,28 +6693,28 @@
         <v>2.876</v>
       </c>
       <c r="M66">
-        <v>0.9148352000000001</v>
+        <v>0.9291295000000002</v>
       </c>
       <c r="N66">
-        <v>1.9611648</v>
+        <v>1.9468705</v>
       </c>
       <c r="O66">
-        <v>0.313786368</v>
+        <v>0.31149928</v>
       </c>
       <c r="P66">
-        <v>1.647378432</v>
+        <v>1.63537122</v>
       </c>
       <c r="Q66">
-        <v>2.421378432</v>
+        <v>2.40937122</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1506039383260895</v>
+        <v>0.1534061826663593</v>
       </c>
       <c r="T66">
-        <v>1.442665659783226</v>
+        <v>1.481239607905772</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.143735614895447</v>
+        <v>3.095370451589363</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08869076393322575</v>
+        <v>0.08870395006905929</v>
       </c>
       <c r="C67">
-        <v>7.696529442248142</v>
+        <v>7.471870098848042</v>
       </c>
       <c r="D67">
-        <v>19.37152944224814</v>
+        <v>19.36987009884804</v>
       </c>
       <c r="E67">
-        <v>14.495</v>
+        <v>14.718</v>
       </c>
       <c r="F67">
-        <v>14.495</v>
+        <v>14.718</v>
       </c>
       <c r="G67">
         <v>2.82</v>
@@ -6775,28 +6775,28 @@
         <v>2.876</v>
       </c>
       <c r="M67">
-        <v>0.9291295000000002</v>
+        <v>0.9434238000000001</v>
       </c>
       <c r="N67">
-        <v>1.9468705</v>
+        <v>1.9325762</v>
       </c>
       <c r="O67">
-        <v>0.31149928</v>
+        <v>0.3092121919999999</v>
       </c>
       <c r="P67">
-        <v>1.63537122</v>
+        <v>1.623364008</v>
       </c>
       <c r="Q67">
-        <v>2.40937122</v>
+        <v>2.397364008</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1534061826663593</v>
+        <v>0.1563732649089979</v>
       </c>
       <c r="T67">
-        <v>1.481239607905772</v>
+        <v>1.522082611800233</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.095370451589363</v>
+        <v>3.048470899292555</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08870395006905929</v>
+        <v>0.08871713620489281</v>
       </c>
       <c r="C68">
-        <v>7.471870098848042</v>
+        <v>7.247211039698572</v>
       </c>
       <c r="D68">
-        <v>19.36987009884804</v>
+        <v>19.36821103969857</v>
       </c>
       <c r="E68">
-        <v>14.718</v>
+        <v>14.941</v>
       </c>
       <c r="F68">
-        <v>14.718</v>
+        <v>14.941</v>
       </c>
       <c r="G68">
         <v>2.82</v>
@@ -6857,28 +6857,28 @@
         <v>2.876</v>
       </c>
       <c r="M68">
-        <v>0.9434238000000001</v>
+        <v>0.9577181000000001</v>
       </c>
       <c r="N68">
-        <v>1.9325762</v>
+        <v>1.9182819</v>
       </c>
       <c r="O68">
-        <v>0.3092121919999999</v>
+        <v>0.3069251039999999</v>
       </c>
       <c r="P68">
-        <v>1.623364008</v>
+        <v>1.611356796</v>
       </c>
       <c r="Q68">
-        <v>2.397364008</v>
+        <v>2.385356796</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1563732649089979</v>
+        <v>0.159520170317857</v>
       </c>
       <c r="T68">
-        <v>1.522082611800233</v>
+        <v>1.565400949264055</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.048470899292555</v>
+        <v>3.002971333631472</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08871713620489281</v>
+        <v>0.09318568234072633</v>
       </c>
       <c r="C69">
-        <v>7.247211039698572</v>
+        <v>6.477891017708824</v>
       </c>
       <c r="D69">
-        <v>19.36821103969857</v>
+        <v>18.82189101770883</v>
       </c>
       <c r="E69">
-        <v>14.941</v>
+        <v>15.164</v>
       </c>
       <c r="F69">
-        <v>14.941</v>
+        <v>15.164</v>
       </c>
       <c r="G69">
         <v>2.82</v>
@@ -6939,45 +6939,45 @@
         <v>2.876</v>
       </c>
       <c r="M69">
-        <v>0.9577181000000001</v>
+        <v>1.0902916</v>
       </c>
       <c r="N69">
-        <v>1.9182819</v>
+        <v>1.7857084</v>
       </c>
       <c r="O69">
-        <v>0.3069251039999999</v>
+        <v>0.2857133439999999</v>
       </c>
       <c r="P69">
-        <v>1.611356796</v>
+        <v>1.499995056</v>
       </c>
       <c r="Q69">
-        <v>2.385356796</v>
+        <v>2.273995056</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.159520170317857</v>
+        <v>0.1628637573147698</v>
       </c>
       <c r="T69">
-        <v>1.565400949264055</v>
+        <v>1.611426682819365</v>
       </c>
       <c r="U69">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V69">
         <v>0.16</v>
       </c>
       <c r="W69">
-        <v>0.053844</v>
+        <v>0.06039600000000001</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y69">
-        <v>3.002971333631472</v>
+        <v>2.637826431020838</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09318568234072633</v>
+        <v>0.09326438847655985</v>
       </c>
       <c r="C70">
-        <v>6.477891017708824</v>
+        <v>6.245544550330271</v>
       </c>
       <c r="D70">
-        <v>18.82189101770883</v>
+        <v>18.81254455033027</v>
       </c>
       <c r="E70">
-        <v>15.164</v>
+        <v>15.387</v>
       </c>
       <c r="F70">
-        <v>15.164</v>
+        <v>15.387</v>
       </c>
       <c r="G70">
         <v>2.82</v>
@@ -7021,28 +7021,28 @@
         <v>2.876</v>
       </c>
       <c r="M70">
-        <v>1.0902916</v>
+        <v>1.1063253</v>
       </c>
       <c r="N70">
-        <v>1.7857084</v>
+        <v>1.7696747</v>
       </c>
       <c r="O70">
-        <v>0.2857133439999999</v>
+        <v>0.283147952</v>
       </c>
       <c r="P70">
-        <v>1.499995056</v>
+        <v>1.486526748</v>
       </c>
       <c r="Q70">
-        <v>2.273995056</v>
+        <v>2.260526748</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1628637573147698</v>
+        <v>0.166423059601806</v>
       </c>
       <c r="T70">
-        <v>1.611426682819365</v>
+        <v>1.660421818539535</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.637826431020838</v>
+        <v>2.599597062455319</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09326438847655985</v>
+        <v>0.09334309461239337</v>
       </c>
       <c r="C71">
-        <v>6.245544550330271</v>
+        <v>6.013207360775604</v>
       </c>
       <c r="D71">
-        <v>18.81254455033027</v>
+        <v>18.80320736077561</v>
       </c>
       <c r="E71">
-        <v>15.387</v>
+        <v>15.61</v>
       </c>
       <c r="F71">
-        <v>15.387</v>
+        <v>15.61</v>
       </c>
       <c r="G71">
         <v>2.82</v>
@@ -7103,28 +7103,28 @@
         <v>2.876</v>
       </c>
       <c r="M71">
-        <v>1.1063253</v>
+        <v>1.122359</v>
       </c>
       <c r="N71">
-        <v>1.7696747</v>
+        <v>1.753641</v>
       </c>
       <c r="O71">
-        <v>0.283147952</v>
+        <v>0.28058256</v>
       </c>
       <c r="P71">
-        <v>1.486526748</v>
+        <v>1.47305844</v>
       </c>
       <c r="Q71">
-        <v>2.260526748</v>
+        <v>2.24705844</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.166423059601806</v>
+        <v>0.1702196487079779</v>
       </c>
       <c r="T71">
-        <v>1.660421818539535</v>
+        <v>1.712683296641049</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.599597062455319</v>
+        <v>2.5624599615631</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09334309461239337</v>
+        <v>0.09342180074822692</v>
       </c>
       <c r="C72">
-        <v>6.013207360775604</v>
+        <v>5.780879435237143</v>
       </c>
       <c r="D72">
-        <v>18.80320736077561</v>
+        <v>18.79387943523714</v>
       </c>
       <c r="E72">
-        <v>15.61</v>
+        <v>15.833</v>
       </c>
       <c r="F72">
-        <v>15.61</v>
+        <v>15.833</v>
       </c>
       <c r="G72">
         <v>2.82</v>
@@ -7185,28 +7185,28 @@
         <v>2.876</v>
       </c>
       <c r="M72">
-        <v>1.122359</v>
+        <v>1.1383927</v>
       </c>
       <c r="N72">
-        <v>1.753641</v>
+        <v>1.7376073</v>
       </c>
       <c r="O72">
-        <v>0.28058256</v>
+        <v>0.2780171679999999</v>
       </c>
       <c r="P72">
-        <v>1.47305844</v>
+        <v>1.459590132</v>
       </c>
       <c r="Q72">
-        <v>2.24705844</v>
+        <v>2.233590132</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1702196487079779</v>
+        <v>0.1742780715456101</v>
       </c>
       <c r="T72">
-        <v>1.712683296641049</v>
+        <v>1.768549014611634</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.5624599615631</v>
+        <v>2.526368976188972</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09342180074822691</v>
+        <v>0.09585922688406044</v>
       </c>
       <c r="C73">
-        <v>5.780879435237148</v>
+        <v>5.273517729096259</v>
       </c>
       <c r="D73">
-        <v>18.79387943523715</v>
+        <v>18.50951772909626</v>
       </c>
       <c r="E73">
-        <v>15.833</v>
+        <v>16.056</v>
       </c>
       <c r="F73">
-        <v>15.833</v>
+        <v>16.056</v>
       </c>
       <c r="G73">
         <v>2.82</v>
@@ -7267,45 +7267,45 @@
         <v>2.876</v>
       </c>
       <c r="M73">
-        <v>1.1383927</v>
+        <v>1.2170448</v>
       </c>
       <c r="N73">
-        <v>1.7376073</v>
+        <v>1.6589552</v>
       </c>
       <c r="O73">
-        <v>0.278017168</v>
+        <v>0.265432832</v>
       </c>
       <c r="P73">
-        <v>1.459590132</v>
+        <v>1.393522368</v>
       </c>
       <c r="Q73">
-        <v>2.233590132</v>
+        <v>2.167522368</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.17427807154561</v>
+        <v>0.1786263817287873</v>
       </c>
       <c r="T73">
-        <v>1.768549014611633</v>
+        <v>1.828405141008687</v>
       </c>
       <c r="U73">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V73">
         <v>0.16</v>
       </c>
       <c r="W73">
-        <v>0.06039600000000001</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.526368976188972</v>
+        <v>2.363101177540876</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09585922688406044</v>
+        <v>0.09597069301989397</v>
       </c>
       <c r="C74">
-        <v>5.273517729096259</v>
+        <v>5.037719176427846</v>
       </c>
       <c r="D74">
-        <v>18.50951772909626</v>
+        <v>18.49671917642785</v>
       </c>
       <c r="E74">
-        <v>16.056</v>
+        <v>16.279</v>
       </c>
       <c r="F74">
-        <v>16.056</v>
+        <v>16.279</v>
       </c>
       <c r="G74">
         <v>2.82</v>
@@ -7349,28 +7349,28 @@
         <v>2.876</v>
       </c>
       <c r="M74">
-        <v>1.2170448</v>
+        <v>1.2339482</v>
       </c>
       <c r="N74">
-        <v>1.6589552</v>
+        <v>1.6420518</v>
       </c>
       <c r="O74">
-        <v>0.265432832</v>
+        <v>0.262728288</v>
       </c>
       <c r="P74">
-        <v>1.393522368</v>
+        <v>1.379323512</v>
       </c>
       <c r="Q74">
-        <v>2.167522368</v>
+        <v>2.153323512</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1786263817287873</v>
+        <v>0.1832967889625702</v>
       </c>
       <c r="T74">
-        <v>1.828405141008687</v>
+        <v>1.892695054546264</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.363101177540876</v>
+        <v>2.330729928533466</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09597069301989397</v>
+        <v>0.09608215915572749</v>
       </c>
       <c r="C75">
-        <v>5.037719176427846</v>
+        <v>4.801938310850826</v>
       </c>
       <c r="D75">
-        <v>18.49671917642785</v>
+        <v>18.48393831085082</v>
       </c>
       <c r="E75">
-        <v>16.279</v>
+        <v>16.502</v>
       </c>
       <c r="F75">
-        <v>16.279</v>
+        <v>16.502</v>
       </c>
       <c r="G75">
         <v>2.82</v>
@@ -7431,28 +7431,28 @@
         <v>2.876</v>
       </c>
       <c r="M75">
-        <v>1.2339482</v>
+        <v>1.2508516</v>
       </c>
       <c r="N75">
-        <v>1.6420518</v>
+        <v>1.6251484</v>
       </c>
       <c r="O75">
-        <v>0.262728288</v>
+        <v>0.260023744</v>
       </c>
       <c r="P75">
-        <v>1.379323512</v>
+        <v>1.365124656</v>
       </c>
       <c r="Q75">
-        <v>2.153323512</v>
+        <v>2.139124656</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1832967889625702</v>
+        <v>0.1883264582912595</v>
       </c>
       <c r="T75">
-        <v>1.892695054546264</v>
+        <v>1.96193034604827</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.330729928533466</v>
+        <v>2.299233578147879</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09608215915572749</v>
+        <v>0.096193625291561</v>
       </c>
       <c r="C76">
-        <v>4.801938310850826</v>
+        <v>4.566175095726219</v>
       </c>
       <c r="D76">
-        <v>18.48393831085082</v>
+        <v>18.47117509572622</v>
       </c>
       <c r="E76">
-        <v>16.502</v>
+        <v>16.725</v>
       </c>
       <c r="F76">
-        <v>16.502</v>
+        <v>16.725</v>
       </c>
       <c r="G76">
         <v>2.82</v>
@@ -7513,28 +7513,28 @@
         <v>2.876</v>
       </c>
       <c r="M76">
-        <v>1.2508516</v>
+        <v>1.267755</v>
       </c>
       <c r="N76">
-        <v>1.6251484</v>
+        <v>1.608245</v>
       </c>
       <c r="O76">
-        <v>0.260023744</v>
+        <v>0.2573192</v>
       </c>
       <c r="P76">
-        <v>1.365124656</v>
+        <v>1.3509258</v>
       </c>
       <c r="Q76">
-        <v>2.139124656</v>
+        <v>2.1249258</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1883264582912595</v>
+        <v>0.193758501166244</v>
       </c>
       <c r="T76">
-        <v>1.96193034604827</v>
+        <v>2.036704460870436</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.299233578147879</v>
+        <v>2.26857713043924</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.096193625291561</v>
+        <v>0.09630509142739455</v>
       </c>
       <c r="C77">
-        <v>4.566175095726219</v>
+        <v>4.330429494516192</v>
       </c>
       <c r="D77">
-        <v>18.47117509572622</v>
+        <v>18.45842949451619</v>
       </c>
       <c r="E77">
-        <v>16.725</v>
+        <v>16.948</v>
       </c>
       <c r="F77">
-        <v>16.725</v>
+        <v>16.948</v>
       </c>
       <c r="G77">
         <v>2.82</v>
@@ -7595,28 +7595,28 @@
         <v>2.876</v>
       </c>
       <c r="M77">
-        <v>1.267755</v>
+        <v>1.2846584</v>
       </c>
       <c r="N77">
-        <v>1.608245</v>
+        <v>1.5913416</v>
       </c>
       <c r="O77">
-        <v>0.2573192</v>
+        <v>0.254614656</v>
       </c>
       <c r="P77">
-        <v>1.3509258</v>
+        <v>1.336726944</v>
       </c>
       <c r="Q77">
-        <v>2.1249258</v>
+        <v>2.110726944</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.193758501166244</v>
+        <v>0.1996432142808106</v>
       </c>
       <c r="T77">
-        <v>2.036704460870436</v>
+        <v>2.117709751927784</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.26857713043924</v>
+        <v>2.238727431354514</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09630509142739455</v>
+        <v>0.09641655756322806</v>
       </c>
       <c r="C78">
-        <v>4.330429494516192</v>
+        <v>4.094701470783679</v>
       </c>
       <c r="D78">
-        <v>18.45842949451619</v>
+        <v>18.44570147078368</v>
       </c>
       <c r="E78">
-        <v>16.948</v>
+        <v>17.171</v>
       </c>
       <c r="F78">
-        <v>16.948</v>
+        <v>17.171</v>
       </c>
       <c r="G78">
         <v>2.82</v>
@@ -7677,28 +7677,28 @@
         <v>2.876</v>
       </c>
       <c r="M78">
-        <v>1.2846584</v>
+        <v>1.3015618</v>
       </c>
       <c r="N78">
-        <v>1.5913416</v>
+        <v>1.5744382</v>
       </c>
       <c r="O78">
-        <v>0.254614656</v>
+        <v>0.251910112</v>
       </c>
       <c r="P78">
-        <v>1.336726944</v>
+        <v>1.322528088</v>
       </c>
       <c r="Q78">
-        <v>2.110726944</v>
+        <v>2.096528088</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1996432142808106</v>
+        <v>0.2060396415792524</v>
       </c>
       <c r="T78">
-        <v>2.117709751927784</v>
+        <v>2.205758981337943</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.238727431354514</v>
+        <v>2.209653049129131</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09641655756322806</v>
+        <v>0.09652802369906158</v>
       </c>
       <c r="C79">
-        <v>4.094701470783679</v>
+        <v>3.858990988192044</v>
       </c>
       <c r="D79">
-        <v>18.44570147078368</v>
+        <v>18.43299098819205</v>
       </c>
       <c r="E79">
-        <v>17.171</v>
+        <v>17.394</v>
       </c>
       <c r="F79">
-        <v>17.171</v>
+        <v>17.394</v>
       </c>
       <c r="G79">
         <v>2.82</v>
@@ -7759,28 +7759,28 @@
         <v>2.876</v>
       </c>
       <c r="M79">
-        <v>1.3015618</v>
+        <v>1.3184652</v>
       </c>
       <c r="N79">
-        <v>1.5744382</v>
+        <v>1.5575348</v>
       </c>
       <c r="O79">
-        <v>0.251910112</v>
+        <v>0.2492055679999999</v>
       </c>
       <c r="P79">
-        <v>1.322528088</v>
+        <v>1.308329232</v>
       </c>
       <c r="Q79">
-        <v>2.096528088</v>
+        <v>2.082329232</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2060396415792524</v>
+        <v>0.2130175622684617</v>
       </c>
       <c r="T79">
-        <v>2.205758981337943</v>
+        <v>2.301812686149026</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.209653049129131</v>
+        <v>2.181324163883885</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09652802369906158</v>
+        <v>0.09663948983489511</v>
       </c>
       <c r="C80">
-        <v>3.858990988192044</v>
+        <v>3.623298010504751</v>
       </c>
       <c r="D80">
-        <v>18.43299098819205</v>
+        <v>18.42029801050475</v>
       </c>
       <c r="E80">
-        <v>17.394</v>
+        <v>17.617</v>
       </c>
       <c r="F80">
-        <v>17.394</v>
+        <v>17.617</v>
       </c>
       <c r="G80">
         <v>2.82</v>
@@ -7841,28 +7841,28 @@
         <v>2.876</v>
       </c>
       <c r="M80">
-        <v>1.3184652</v>
+        <v>1.3353686</v>
       </c>
       <c r="N80">
-        <v>1.5575348</v>
+        <v>1.5406314</v>
       </c>
       <c r="O80">
-        <v>0.2492055679999999</v>
+        <v>0.246501024</v>
       </c>
       <c r="P80">
-        <v>1.308329232</v>
+        <v>1.294130376</v>
       </c>
       <c r="Q80">
-        <v>2.082329232</v>
+        <v>2.068130376</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2130175622684617</v>
+        <v>0.2206600468328339</v>
       </c>
       <c r="T80">
-        <v>2.301812686149026</v>
+        <v>2.407014362846879</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.181324163883885</v>
+        <v>2.153712465606874</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09663948983489511</v>
+        <v>0.09675095597072864</v>
       </c>
       <c r="C81">
-        <v>3.623298010504751</v>
+        <v>3.387622501584982</v>
       </c>
       <c r="D81">
-        <v>18.42029801050475</v>
+        <v>18.40762250158498</v>
       </c>
       <c r="E81">
-        <v>17.617</v>
+        <v>17.84</v>
       </c>
       <c r="F81">
-        <v>17.617</v>
+        <v>17.84</v>
       </c>
       <c r="G81">
         <v>2.82</v>
@@ -7923,28 +7923,28 @@
         <v>2.876</v>
       </c>
       <c r="M81">
-        <v>1.3353686</v>
+        <v>1.352272</v>
       </c>
       <c r="N81">
-        <v>1.5406314</v>
+        <v>1.523728</v>
       </c>
       <c r="O81">
-        <v>0.246501024</v>
+        <v>0.24379648</v>
       </c>
       <c r="P81">
-        <v>1.294130376</v>
+        <v>1.27993152</v>
       </c>
       <c r="Q81">
-        <v>2.068130376</v>
+        <v>2.05393152</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2206600468328339</v>
+        <v>0.2290667798536432</v>
       </c>
       <c r="T81">
-        <v>2.407014362846879</v>
+        <v>2.522736207214519</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.153712465606874</v>
+        <v>2.126791059786788</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09675095597072864</v>
+        <v>0.09686242210656217</v>
       </c>
       <c r="C82">
-        <v>3.387622501584982</v>
+        <v>3.151964425395338</v>
       </c>
       <c r="D82">
-        <v>18.40762250158498</v>
+        <v>18.39496442539534</v>
       </c>
       <c r="E82">
-        <v>17.84</v>
+        <v>18.063</v>
       </c>
       <c r="F82">
-        <v>17.84</v>
+        <v>18.063</v>
       </c>
       <c r="G82">
         <v>2.82</v>
@@ -8005,28 +8005,28 @@
         <v>2.876</v>
       </c>
       <c r="M82">
-        <v>1.352272</v>
+        <v>1.3691754</v>
       </c>
       <c r="N82">
-        <v>1.523728</v>
+        <v>1.5068246</v>
       </c>
       <c r="O82">
-        <v>0.24379648</v>
+        <v>0.241091936</v>
       </c>
       <c r="P82">
-        <v>1.27993152</v>
+        <v>1.265732664</v>
       </c>
       <c r="Q82">
-        <v>2.05393152</v>
+        <v>2.039732664</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2290667798536432</v>
+        <v>0.2383584321398009</v>
       </c>
       <c r="T82">
-        <v>2.522736207214519</v>
+        <v>2.650639298357698</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.126791059786788</v>
+        <v>2.100534380036334</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09686242210656217</v>
+        <v>0.09697388824239569</v>
       </c>
       <c r="C83">
-        <v>3.151964425395338</v>
+        <v>2.91632374599747</v>
       </c>
       <c r="D83">
-        <v>18.39496442539534</v>
+        <v>18.38232374599747</v>
       </c>
       <c r="E83">
-        <v>18.063</v>
+        <v>18.286</v>
       </c>
       <c r="F83">
-        <v>18.063</v>
+        <v>18.286</v>
       </c>
       <c r="G83">
         <v>2.82</v>
@@ -8087,28 +8087,28 @@
         <v>2.876</v>
       </c>
       <c r="M83">
-        <v>1.3691754</v>
+        <v>1.3860788</v>
       </c>
       <c r="N83">
-        <v>1.5068246</v>
+        <v>1.4899212</v>
       </c>
       <c r="O83">
-        <v>0.241091936</v>
+        <v>0.2383873919999999</v>
       </c>
       <c r="P83">
-        <v>1.265732664</v>
+        <v>1.251533808</v>
       </c>
       <c r="Q83">
-        <v>2.039732664</v>
+        <v>2.025533808</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2383584321398009</v>
+        <v>0.2486824902355316</v>
       </c>
       <c r="T83">
-        <v>2.650639298357698</v>
+        <v>2.792753844072342</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.100534380036334</v>
+        <v>2.074918107109061</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09697388824239569</v>
+        <v>0.09708535437822921</v>
       </c>
       <c r="C84">
-        <v>2.91632374599747</v>
+        <v>2.680700427551745</v>
       </c>
       <c r="D84">
-        <v>18.38232374599747</v>
+        <v>18.36970042755175</v>
       </c>
       <c r="E84">
-        <v>18.286</v>
+        <v>18.509</v>
       </c>
       <c r="F84">
-        <v>18.286</v>
+        <v>18.509</v>
       </c>
       <c r="G84">
         <v>2.82</v>
@@ -8169,28 +8169,28 @@
         <v>2.876</v>
       </c>
       <c r="M84">
-        <v>1.3860788</v>
+        <v>1.402982200000001</v>
       </c>
       <c r="N84">
-        <v>1.4899212</v>
+        <v>1.473017799999999</v>
       </c>
       <c r="O84">
-        <v>0.2383873919999999</v>
+        <v>0.2356828479999999</v>
       </c>
       <c r="P84">
-        <v>1.251533808</v>
+        <v>1.237334951999999</v>
       </c>
       <c r="Q84">
-        <v>2.025533808</v>
+        <v>2.011334951999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2486824902355316</v>
+        <v>0.2602211434013484</v>
       </c>
       <c r="T84">
-        <v>2.792753844072342</v>
+        <v>2.951587748106356</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.074918107109061</v>
+        <v>2.049919093770398</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09708535437822921</v>
+        <v>0.09719682051406274</v>
       </c>
       <c r="C85">
-        <v>2.680700427551745</v>
+        <v>2.445094434316907</v>
       </c>
       <c r="D85">
-        <v>18.36970042755175</v>
+        <v>18.35709443431691</v>
       </c>
       <c r="E85">
-        <v>18.509</v>
+        <v>18.732</v>
       </c>
       <c r="F85">
-        <v>18.509</v>
+        <v>18.732</v>
       </c>
       <c r="G85">
         <v>2.82</v>
@@ -8251,28 +8251,28 @@
         <v>2.876</v>
       </c>
       <c r="M85">
-        <v>1.402982200000001</v>
+        <v>1.4198856</v>
       </c>
       <c r="N85">
-        <v>1.473017799999999</v>
+        <v>1.456114399999999</v>
       </c>
       <c r="O85">
-        <v>0.2356828479999999</v>
+        <v>0.2329783039999999</v>
       </c>
       <c r="P85">
-        <v>1.237334951999999</v>
+        <v>1.223136096</v>
       </c>
       <c r="Q85">
-        <v>2.011334951999999</v>
+        <v>1.997136096</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2602211434013484</v>
+        <v>0.2732021282128922</v>
       </c>
       <c r="T85">
-        <v>2.951587748106356</v>
+        <v>3.130275890144621</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.049919093770398</v>
+        <v>2.025515295035036</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09719682051406274</v>
+        <v>0.09730828664989627</v>
       </c>
       <c r="C86">
-        <v>2.445094434316911</v>
+        <v>2.209505730649745</v>
       </c>
       <c r="D86">
-        <v>18.35709443431691</v>
+        <v>18.34450573064975</v>
       </c>
       <c r="E86">
-        <v>18.732</v>
+        <v>18.955</v>
       </c>
       <c r="F86">
-        <v>18.732</v>
+        <v>18.955</v>
       </c>
       <c r="G86">
         <v>2.82</v>
@@ -8333,28 +8333,28 @@
         <v>2.876</v>
       </c>
       <c r="M86">
-        <v>1.4198856</v>
+        <v>1.436789</v>
       </c>
       <c r="N86">
-        <v>1.4561144</v>
+        <v>1.439211</v>
       </c>
       <c r="O86">
-        <v>0.232978304</v>
+        <v>0.2302737599999999</v>
       </c>
       <c r="P86">
-        <v>1.223136096</v>
+        <v>1.20893724</v>
       </c>
       <c r="Q86">
-        <v>1.997136096</v>
+        <v>1.98293724</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2732021282128921</v>
+        <v>0.2879139109993084</v>
       </c>
       <c r="T86">
-        <v>3.130275890144619</v>
+        <v>3.332789117787986</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.025515295035037</v>
+        <v>2.001685703328742</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09730828664989627</v>
+        <v>0.1076778327857298</v>
       </c>
       <c r="C87">
-        <v>2.209505730649745</v>
+        <v>0.886382064757484</v>
       </c>
       <c r="D87">
-        <v>18.34450573064975</v>
+        <v>17.24438206475748</v>
       </c>
       <c r="E87">
-        <v>18.955</v>
+        <v>19.178</v>
       </c>
       <c r="F87">
-        <v>18.955</v>
+        <v>19.178</v>
       </c>
       <c r="G87">
         <v>2.82</v>
@@ -8415,45 +8415,45 @@
         <v>2.876</v>
       </c>
       <c r="M87">
-        <v>1.436789</v>
+        <v>1.72602</v>
       </c>
       <c r="N87">
-        <v>1.439211</v>
+        <v>1.14998</v>
       </c>
       <c r="O87">
-        <v>0.2302737599999999</v>
+        <v>0.1839968</v>
       </c>
       <c r="P87">
-        <v>1.20893724</v>
+        <v>0.9659831999999998</v>
       </c>
       <c r="Q87">
-        <v>1.98293724</v>
+        <v>1.7399832</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2879139109993084</v>
+        <v>0.304727377040927</v>
       </c>
       <c r="T87">
-        <v>3.332789117787986</v>
+        <v>3.564232806523263</v>
       </c>
       <c r="U87">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V87">
         <v>0.16</v>
       </c>
       <c r="W87">
-        <v>0.06367200000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y87">
-        <v>2.001685703328742</v>
+        <v>1.666261109373008</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1076778327857298</v>
+        <v>0.1079085789215633</v>
       </c>
       <c r="C88">
-        <v>0.886382064757484</v>
+        <v>0.6404005500616066</v>
       </c>
       <c r="D88">
-        <v>17.24438206475748</v>
+        <v>17.22140055006161</v>
       </c>
       <c r="E88">
-        <v>19.178</v>
+        <v>19.401</v>
       </c>
       <c r="F88">
-        <v>19.178</v>
+        <v>19.401</v>
       </c>
       <c r="G88">
         <v>2.82</v>
@@ -8497,28 +8497,28 @@
         <v>2.876</v>
       </c>
       <c r="M88">
-        <v>1.72602</v>
+        <v>1.74609</v>
       </c>
       <c r="N88">
-        <v>1.14998</v>
+        <v>1.12991</v>
       </c>
       <c r="O88">
-        <v>0.1839968</v>
+        <v>0.1807856</v>
       </c>
       <c r="P88">
-        <v>0.9659831999999998</v>
+        <v>0.9491244</v>
       </c>
       <c r="Q88">
-        <v>1.7399832</v>
+        <v>1.7231244</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.304727377040927</v>
+        <v>0.3241275301658716</v>
       </c>
       <c r="T88">
-        <v>3.564232806523263</v>
+        <v>3.831283216602429</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.666261109373008</v>
+        <v>1.647108682828491</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1079085789215633</v>
+        <v>0.1081393250573968</v>
       </c>
       <c r="C89">
-        <v>0.6404005500616066</v>
+        <v>0.394480208574393</v>
       </c>
       <c r="D89">
-        <v>17.22140055006161</v>
+        <v>17.1984802085744</v>
       </c>
       <c r="E89">
-        <v>19.401</v>
+        <v>19.624</v>
       </c>
       <c r="F89">
-        <v>19.401</v>
+        <v>19.624</v>
       </c>
       <c r="G89">
         <v>2.82</v>
@@ -8579,28 +8579,28 @@
         <v>2.876</v>
       </c>
       <c r="M89">
-        <v>1.74609</v>
+        <v>1.76616</v>
       </c>
       <c r="N89">
-        <v>1.12991</v>
+        <v>1.10984</v>
       </c>
       <c r="O89">
-        <v>0.1807856</v>
+        <v>0.1775744</v>
       </c>
       <c r="P89">
-        <v>0.9491244</v>
+        <v>0.9322655999999998</v>
       </c>
       <c r="Q89">
-        <v>1.7231244</v>
+        <v>1.7062656</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3241275301658716</v>
+        <v>0.3467610421449737</v>
       </c>
       <c r="T89">
-        <v>3.831283216602429</v>
+        <v>4.142842028361456</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.647108682828491</v>
+        <v>1.62839153870544</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1081393250573968</v>
+        <v>0.1083700711932304</v>
       </c>
       <c r="C90">
-        <v>0.394480208574393</v>
+        <v>0.1486207963701887</v>
       </c>
       <c r="D90">
-        <v>17.1984802085744</v>
+        <v>17.17562079637019</v>
       </c>
       <c r="E90">
-        <v>19.624</v>
+        <v>19.847</v>
       </c>
       <c r="F90">
-        <v>19.624</v>
+        <v>19.847</v>
       </c>
       <c r="G90">
         <v>2.82</v>
@@ -8661,28 +8661,28 @@
         <v>2.876</v>
       </c>
       <c r="M90">
-        <v>1.76616</v>
+        <v>1.78623</v>
       </c>
       <c r="N90">
-        <v>1.10984</v>
+        <v>1.08977</v>
       </c>
       <c r="O90">
-        <v>0.1775744</v>
+        <v>0.1743632</v>
       </c>
       <c r="P90">
-        <v>0.9322655999999998</v>
+        <v>0.9154068</v>
       </c>
       <c r="Q90">
-        <v>1.7062656</v>
+        <v>1.6894068</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3467610421449737</v>
+        <v>0.373509738120276</v>
       </c>
       <c r="T90">
-        <v>4.142842028361456</v>
+        <v>4.511047896803943</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.62839153870544</v>
+        <v>1.610095004562682</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1083700711932304</v>
+        <v>0.1086008173290639</v>
       </c>
       <c r="C91">
-        <v>0.1486207963701887</v>
+        <v>-0.097177929181548</v>
       </c>
       <c r="D91">
-        <v>17.17562079637019</v>
+        <v>17.15282207081845</v>
       </c>
       <c r="E91">
-        <v>19.847</v>
+        <v>20.07</v>
       </c>
       <c r="F91">
-        <v>19.847</v>
+        <v>20.07</v>
       </c>
       <c r="G91">
         <v>2.82</v>
@@ -8743,28 +8743,28 @@
         <v>2.876</v>
       </c>
       <c r="M91">
-        <v>1.78623</v>
+        <v>1.8063</v>
       </c>
       <c r="N91">
-        <v>1.08977</v>
+        <v>1.0697</v>
       </c>
       <c r="O91">
-        <v>0.1743632</v>
+        <v>0.171152</v>
       </c>
       <c r="P91">
-        <v>0.9154068</v>
+        <v>0.8985479999999999</v>
       </c>
       <c r="Q91">
-        <v>1.6894068</v>
+        <v>1.672548</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.373509738120276</v>
+        <v>0.405608173290639</v>
       </c>
       <c r="T91">
-        <v>4.511047896803943</v>
+        <v>4.952894938934927</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.610095004562682</v>
+        <v>1.592205060067541</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1086008173290639</v>
+        <v>0.1088315634648974</v>
       </c>
       <c r="C92">
-        <v>-0.097177929181548</v>
+        <v>-0.3429162094247964</v>
       </c>
       <c r="D92">
-        <v>17.15282207081845</v>
+        <v>17.13008379057521</v>
       </c>
       <c r="E92">
-        <v>20.07</v>
+        <v>20.293</v>
       </c>
       <c r="F92">
-        <v>20.07</v>
+        <v>20.293</v>
       </c>
       <c r="G92">
         <v>2.82</v>
@@ -8825,28 +8825,28 @@
         <v>2.876</v>
       </c>
       <c r="M92">
-        <v>1.8063</v>
+        <v>1.82637</v>
       </c>
       <c r="N92">
-        <v>1.0697</v>
+        <v>1.04963</v>
       </c>
       <c r="O92">
-        <v>0.171152</v>
+        <v>0.1679407999999999</v>
       </c>
       <c r="P92">
-        <v>0.8985479999999999</v>
+        <v>0.8816891999999996</v>
       </c>
       <c r="Q92">
-        <v>1.672548</v>
+        <v>1.6556892</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.405608173290639</v>
+        <v>0.4448395940544159</v>
       </c>
       <c r="T92">
-        <v>4.952894938934927</v>
+        <v>5.492930212650573</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.592205060067541</v>
+        <v>1.5747083011657</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1088315634648974</v>
+        <v>0.1090623096007309</v>
       </c>
       <c r="C93">
-        <v>-0.3429162094247964</v>
+        <v>-0.5885942844254899</v>
       </c>
       <c r="D93">
-        <v>17.13008379057521</v>
+        <v>17.10740571557451</v>
       </c>
       <c r="E93">
-        <v>20.293</v>
+        <v>20.516</v>
       </c>
       <c r="F93">
-        <v>20.293</v>
+        <v>20.516</v>
       </c>
       <c r="G93">
         <v>2.82</v>
@@ -8907,28 +8907,28 @@
         <v>2.876</v>
       </c>
       <c r="M93">
-        <v>1.82637</v>
+        <v>1.84644</v>
       </c>
       <c r="N93">
-        <v>1.04963</v>
+        <v>1.02956</v>
       </c>
       <c r="O93">
-        <v>0.1679407999999999</v>
+        <v>0.1647296</v>
       </c>
       <c r="P93">
-        <v>0.8816891999999996</v>
+        <v>0.8648303999999998</v>
       </c>
       <c r="Q93">
-        <v>1.6556892</v>
+        <v>1.6388304</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4448395940544159</v>
+        <v>0.493878870009137</v>
       </c>
       <c r="T93">
-        <v>5.492930212650573</v>
+        <v>6.167974304795132</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.5747083011657</v>
+        <v>1.557591906587812</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1090623096007309</v>
+        <v>0.1092930557365645</v>
       </c>
       <c r="C94">
-        <v>-0.5885942844254899</v>
+        <v>-0.8342123929799925</v>
       </c>
       <c r="D94">
-        <v>17.10740571557451</v>
+        <v>17.08478760702001</v>
       </c>
       <c r="E94">
-        <v>20.516</v>
+        <v>20.739</v>
       </c>
       <c r="F94">
-        <v>20.516</v>
+        <v>20.739</v>
       </c>
       <c r="G94">
         <v>2.82</v>
@@ -8989,28 +8989,28 @@
         <v>2.876</v>
       </c>
       <c r="M94">
-        <v>1.84644</v>
+        <v>1.86651</v>
       </c>
       <c r="N94">
-        <v>1.02956</v>
+        <v>1.00949</v>
       </c>
       <c r="O94">
-        <v>0.1647296</v>
+        <v>0.1615184</v>
       </c>
       <c r="P94">
-        <v>0.8648303999999998</v>
+        <v>0.8479715999999999</v>
       </c>
       <c r="Q94">
-        <v>1.6388304</v>
+        <v>1.6219716</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.493878870009137</v>
+        <v>0.5569293676652068</v>
       </c>
       <c r="T94">
-        <v>6.167974304795132</v>
+        <v>7.035888137552421</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.557591906587812</v>
+        <v>1.540843606516975</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1092930557365645</v>
+        <v>0.109523801872398</v>
       </c>
       <c r="C95">
-        <v>-0.8342123929799925</v>
+        <v>-1.079770772623455</v>
       </c>
       <c r="D95">
-        <v>17.08478760702001</v>
+        <v>17.06222922737655</v>
       </c>
       <c r="E95">
-        <v>20.739</v>
+        <v>20.962</v>
       </c>
       <c r="F95">
-        <v>20.739</v>
+        <v>20.962</v>
       </c>
       <c r="G95">
         <v>2.82</v>
@@ -9071,28 +9071,28 @@
         <v>2.876</v>
       </c>
       <c r="M95">
-        <v>1.86651</v>
+        <v>1.88658</v>
       </c>
       <c r="N95">
-        <v>1.00949</v>
+        <v>0.9894199999999997</v>
       </c>
       <c r="O95">
-        <v>0.1615184</v>
+        <v>0.1583072</v>
       </c>
       <c r="P95">
-        <v>0.8479715999999999</v>
+        <v>0.8311127999999998</v>
       </c>
       <c r="Q95">
-        <v>1.6219716</v>
+        <v>1.6051128</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5569293676652068</v>
+        <v>0.6409966978733004</v>
       </c>
       <c r="T95">
-        <v>7.035888137552421</v>
+        <v>8.193106581228809</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.540843606516975</v>
+        <v>1.524451653256157</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.109523801872398</v>
+        <v>0.1097545480082315</v>
       </c>
       <c r="C96">
-        <v>-1.079770772623455</v>
+        <v>-1.325269659638131</v>
       </c>
       <c r="D96">
-        <v>17.06222922737655</v>
+        <v>17.03973034036187</v>
       </c>
       <c r="E96">
-        <v>20.962</v>
+        <v>21.185</v>
       </c>
       <c r="F96">
-        <v>20.962</v>
+        <v>21.185</v>
       </c>
       <c r="G96">
         <v>2.82</v>
@@ -9153,28 +9153,28 @@
         <v>2.876</v>
       </c>
       <c r="M96">
-        <v>1.88658</v>
+        <v>1.90665</v>
       </c>
       <c r="N96">
-        <v>0.9894199999999997</v>
+        <v>0.9693499999999997</v>
       </c>
       <c r="O96">
-        <v>0.1583072</v>
+        <v>0.155096</v>
       </c>
       <c r="P96">
-        <v>0.8311127999999998</v>
+        <v>0.8142539999999998</v>
       </c>
       <c r="Q96">
-        <v>1.6051128</v>
+        <v>1.588254</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6409966978733004</v>
+        <v>0.7586909601646312</v>
       </c>
       <c r="T96">
-        <v>8.193106581228809</v>
+        <v>9.813212402375752</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.524451653256157</v>
+        <v>1.508404793748197</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1097545480082315</v>
+        <v>0.1582502152029341</v>
       </c>
       <c r="C97">
-        <v>-1.325269659638131</v>
+        <v>-5.245863093632789</v>
       </c>
       <c r="D97">
-        <v>17.03973034036187</v>
+        <v>13.34213690636721</v>
       </c>
       <c r="E97">
-        <v>21.185</v>
+        <v>21.408</v>
       </c>
       <c r="F97">
-        <v>21.185</v>
+        <v>21.408</v>
       </c>
       <c r="G97">
         <v>2.82</v>
@@ -9235,45 +9235,45 @@
         <v>2.876</v>
       </c>
       <c r="M97">
-        <v>1.90665</v>
+        <v>3.1426944</v>
       </c>
       <c r="N97">
-        <v>0.9693499999999997</v>
+        <v>-0.2666944000000004</v>
       </c>
       <c r="O97">
-        <v>0.155096</v>
+        <v>-0.04267110400000007</v>
       </c>
       <c r="P97">
-        <v>0.8142539999999998</v>
+        <v>-0.2240232960000004</v>
       </c>
       <c r="Q97">
-        <v>1.588254</v>
+        <v>0.5499767039999996</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7586909601646312</v>
+        <v>0.9489298195352363</v>
       </c>
       <c r="T97">
-        <v>9.813212402375752</v>
+        <v>12.43192190846672</v>
       </c>
       <c r="U97">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.16</v>
+        <v>0.1464221274585273</v>
       </c>
       <c r="W97">
-        <v>0.0756</v>
+        <v>0.1253052316890882</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>1.508404793748197</v>
+        <v>0.9151382966157955</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1582502152029341</v>
+        <v>0.1592602152029341</v>
       </c>
       <c r="C98">
-        <v>-5.245863093632789</v>
+        <v>-5.528889447639905</v>
       </c>
       <c r="D98">
-        <v>13.34213690636721</v>
+        <v>13.2821105523601</v>
       </c>
       <c r="E98">
-        <v>21.408</v>
+        <v>21.631</v>
       </c>
       <c r="F98">
-        <v>21.408</v>
+        <v>21.631</v>
       </c>
       <c r="G98">
         <v>2.82</v>
@@ -9317,37 +9317,37 @@
         <v>2.876</v>
       </c>
       <c r="M98">
-        <v>3.1426944</v>
+        <v>3.1754308</v>
       </c>
       <c r="N98">
-        <v>-0.2666944000000004</v>
+        <v>-0.2994308000000006</v>
       </c>
       <c r="O98">
-        <v>-0.04267110400000007</v>
+        <v>-0.04790892800000009</v>
       </c>
       <c r="P98">
-        <v>-0.2240232960000004</v>
+        <v>-0.2515218720000005</v>
       </c>
       <c r="Q98">
-        <v>0.5499767039999996</v>
+        <v>0.5224781279999995</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9489298195352338</v>
+        <v>1.249973092713645</v>
       </c>
       <c r="T98">
-        <v>12.43192190846669</v>
+        <v>16.57589587795559</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1464221274585273</v>
+        <v>0.1449126209898827</v>
       </c>
       <c r="W98">
-        <v>0.1253052316890882</v>
+        <v>0.1255268272386852</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.9151382966157955</v>
+        <v>0.9057038811867667</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1592602152029341</v>
+        <v>0.1602702152029341</v>
       </c>
       <c r="C99">
-        <v>-5.528889447639905</v>
+        <v>-5.811378102903106</v>
       </c>
       <c r="D99">
-        <v>13.2821105523601</v>
+        <v>13.22262189709689</v>
       </c>
       <c r="E99">
-        <v>21.631</v>
+        <v>21.854</v>
       </c>
       <c r="F99">
-        <v>21.631</v>
+        <v>21.854</v>
       </c>
       <c r="G99">
         <v>2.82</v>
@@ -9399,37 +9399,37 @@
         <v>2.876</v>
       </c>
       <c r="M99">
-        <v>3.1754308</v>
+        <v>3.2081672</v>
       </c>
       <c r="N99">
-        <v>-0.2994308000000006</v>
+        <v>-0.3321672000000002</v>
       </c>
       <c r="O99">
-        <v>-0.04790892800000009</v>
+        <v>-0.05314675200000003</v>
       </c>
       <c r="P99">
-        <v>-0.2515218720000005</v>
+        <v>-0.2790204480000002</v>
       </c>
       <c r="Q99">
-        <v>0.5224781279999995</v>
+        <v>0.4949795519999998</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.249973092713645</v>
+        <v>1.852059639070468</v>
       </c>
       <c r="T99">
-        <v>16.57589587795559</v>
+        <v>24.86384381693338</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1449126209898827</v>
+        <v>0.1434339207757002</v>
       </c>
       <c r="W99">
-        <v>0.1255268272386852</v>
+        <v>0.1257439004301272</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.9057038811867667</v>
+        <v>0.8964620048481263</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1602702152029341</v>
+        <v>0.1612802152029341</v>
       </c>
       <c r="C100">
-        <v>-5.811378102903106</v>
+        <v>-6.093336252032836</v>
       </c>
       <c r="D100">
-        <v>13.22262189709689</v>
+        <v>13.16366374796717</v>
       </c>
       <c r="E100">
-        <v>21.854</v>
+        <v>22.077</v>
       </c>
       <c r="F100">
-        <v>21.854</v>
+        <v>22.077</v>
       </c>
       <c r="G100">
         <v>2.82</v>
@@ -9481,37 +9481,37 @@
         <v>2.876</v>
       </c>
       <c r="M100">
-        <v>3.2081672</v>
+        <v>3.240903600000001</v>
       </c>
       <c r="N100">
-        <v>-0.3321672000000002</v>
+        <v>-0.3649036000000008</v>
       </c>
       <c r="O100">
-        <v>-0.05314675200000003</v>
+        <v>-0.05838457600000013</v>
       </c>
       <c r="P100">
-        <v>-0.2790204480000002</v>
+        <v>-0.3065190240000006</v>
       </c>
       <c r="Q100">
-        <v>0.4949795519999998</v>
+        <v>0.4674809759999994</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.852059639070468</v>
+        <v>3.658319278140936</v>
       </c>
       <c r="T100">
-        <v>24.86384381693338</v>
+        <v>49.72768763386676</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1434339207757002</v>
+        <v>0.1419850932931173</v>
       </c>
       <c r="W100">
-        <v>0.1257439004301272</v>
+        <v>0.1259565883045704</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8964620048481263</v>
+        <v>0.8874068330819834</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1612802152029341</v>
-      </c>
-      <c r="C101">
-        <v>-6.093336252032836</v>
-      </c>
-      <c r="D101">
-        <v>13.16366374796717</v>
-      </c>
-      <c r="E101">
-        <v>22.077</v>
-      </c>
-      <c r="F101">
-        <v>22.077</v>
-      </c>
-      <c r="G101">
-        <v>2.82</v>
-      </c>
-      <c r="H101">
-        <v>22.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.65</v>
-      </c>
-      <c r="K101">
-        <v>0.774</v>
-      </c>
-      <c r="L101">
-        <v>2.876</v>
-      </c>
-      <c r="M101">
-        <v>3.240903600000001</v>
-      </c>
-      <c r="N101">
-        <v>-0.3649036000000008</v>
-      </c>
-      <c r="O101">
-        <v>-0.05838457600000013</v>
-      </c>
-      <c r="P101">
-        <v>-0.3065190240000006</v>
-      </c>
-      <c r="Q101">
-        <v>0.4674809759999994</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.658319278140936</v>
-      </c>
-      <c r="T101">
-        <v>49.72768763386676</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.1419850932931173</v>
-      </c>
-      <c r="W101">
-        <v>0.1259565883045704</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8874068330819834</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
